--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -1271,7 +1271,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>872158</v>
+        <v>872157</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>14666</v>
+        <v>872157</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>851</v>
+        <v>14664</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>872153</v>
+        <v>851</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>14656</v>
+        <v>872156</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>851</v>
+        <v>872156</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>872154</v>
+        <v>14662</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>872154</v>
+        <v>1834</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,23 +2939,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>872154</v>
+        <v>13580</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,23 +2964,23 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>872154</v>
+        <v>3878</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>872154</v>
+        <v>851</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3039,23 +3039,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3064,23 +3064,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3114,23 +3114,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3139,23 +3139,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3164,23 +3164,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3289,23 +3289,23 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3314,23 +3314,23 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3364,23 +3364,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3389,23 +3389,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3414,23 +3414,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3439,23 +3439,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3489,23 +3489,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3539,23 +3539,23 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3614,23 +3614,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3639,23 +3639,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3664,23 +3664,23 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>14658</v>
+        <v>872152</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>851</v>
+        <v>872152</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>872156</v>
+        <v>872152</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>872156</v>
+        <v>872152</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>872156</v>
+        <v>872152</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>872156</v>
+        <v>14654</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>872156</v>
+        <v>851</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>872156</v>
+        <v>872157</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>14662</v>
+        <v>872157</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1834</v>
+        <v>872157</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>13580</v>
+        <v>14664</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,23 +4564,23 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3878</v>
+        <v>851</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,23 +4589,23 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>851</v>
+        <v>872158</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4614,23 +4614,23 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4639,23 +4639,23 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4664,23 +4664,23 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4689,23 +4689,23 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4739,23 +4739,23 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4764,23 +4764,23 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4789,23 +4789,23 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -4814,23 +4814,23 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4839,23 +4839,23 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4864,23 +4864,23 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -4889,23 +4889,23 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4914,23 +4914,23 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4939,23 +4939,23 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -4989,23 +4989,23 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5014,23 +5014,23 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5039,23 +5039,23 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5064,23 +5064,23 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -5114,23 +5114,23 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -5139,23 +5139,23 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -5164,23 +5164,23 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -5189,23 +5189,23 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -5214,23 +5214,23 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -5239,23 +5239,23 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -5264,23 +5264,23 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,23 +5314,23 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>872152</v>
+        <v>872158</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5339,23 +5339,23 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>872152</v>
+        <v>14666</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>872152</v>
+        <v>851</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>14654</v>
+        <v>872154</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>851</v>
+        <v>872154</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,23 +6139,23 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,23 +6164,23 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>872157</v>
+        <v>14658</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6189,23 +6189,23 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>872157</v>
+        <v>851</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6214,23 +6214,23 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>14664</v>
+        <v>872153</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6239,23 +6239,23 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>851</v>
+        <v>872153</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6264,23 +6264,23 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NR01NOVEMBER2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6289,23 +6289,23 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>NR02NOVEMBER2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6314,23 +6314,23 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>NR03NOVEMBER2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6339,23 +6339,23 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>NR04NOVEMBER2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>NR05NOVEMBER2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6389,23 +6389,23 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>NR06NOVEMBER2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6414,23 +6414,23 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>NR07NOVEMBER2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>NR08NOVEMBER2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>NR09NOVEMBER2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>NR10NOVEMBER2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -6514,23 +6514,23 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>NR11NOVEMBER2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -6539,23 +6539,23 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>NR12NOVEMBER2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -6564,23 +6564,23 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>NR13NOVEMBER2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>NR14NOVEMBER2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -6614,23 +6614,23 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>NR15NOVEMBER2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>NR16NOVEMBER2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -6664,23 +6664,23 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>NR17NOVEMBER2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -6689,23 +6689,23 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>NR18NOVEMBER2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>NR19NOVEMBER2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>NR20NOVEMBER2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -6764,23 +6764,23 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>NR21NOVEMBER2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -6789,23 +6789,23 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>NR22NOVEMBER2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -6814,23 +6814,23 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>NR23NOVEMBER2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -6839,23 +6839,23 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>NR24NOVEMBER2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -6864,23 +6864,23 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>NR25NOVEMBER2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -6889,23 +6889,23 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>NR26NOVEMBER2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -6914,23 +6914,23 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>NR27NOVEMBER2027</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -6939,23 +6939,23 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>NR28NOVEMBER2027</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>584855</v>
+        <v>872153</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -6964,23 +6964,23 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>NR29NOVEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>584855</v>
+        <v>14656</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>NR30NOVEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>584855</v>
+        <v>851</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -7026,11 +7026,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>NR01NOVEMBER2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>14664</v>
+        <v>584855</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>NR02NOVEMBER2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>851</v>
+        <v>584855</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>IF01FEBRUARI2027</t>
+          <t>NR03NOVEMBER2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>IF02FEBRUARI2027</t>
+          <t>NR04NOVEMBER2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>IF03FEBRUARI2027</t>
+          <t>NR05NOVEMBER2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>IF04FEBRUARI2027</t>
+          <t>NR06NOVEMBER2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>IF05FEBRUARI2027</t>
+          <t>NR07NOVEMBER2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>IF06FEBRUARI2027</t>
+          <t>NR08NOVEMBER2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>IF07FEBRUARI2027</t>
+          <t>NR09NOVEMBER2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>IF08FEBRUARI2027</t>
+          <t>NR10NOVEMBER2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>IF09FEBRUARI2027</t>
+          <t>NR11NOVEMBER2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>IF10FEBRUARI2027</t>
+          <t>NR12NOVEMBER2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>IF11FEBRUARI2027</t>
+          <t>NR13NOVEMBER2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>IF12FEBRUARI2027</t>
+          <t>NR14NOVEMBER2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>IF13FEBRUARI2027</t>
+          <t>NR15NOVEMBER2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>IF14FEBRUARI2027</t>
+          <t>NR16NOVEMBER2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>IF15FEBRUARI2027</t>
+          <t>NR17NOVEMBER2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>IF16FEBRUARI2027</t>
+          <t>NR18NOVEMBER2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>IF17FEBRUARI2027</t>
+          <t>NR19NOVEMBER2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>IF18FEBRUARI2027</t>
+          <t>NR20NOVEMBER2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>IF19FEBRUARI2027</t>
+          <t>NR21NOVEMBER2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>IF20FEBRUARI2027</t>
+          <t>NR22NOVEMBER2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>IF21FEBRUARI2027</t>
+          <t>NR23NOVEMBER2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>IF22FEBRUARI2027</t>
+          <t>NR24NOVEMBER2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>IF23FEBRUARI2027</t>
+          <t>NR25NOVEMBER2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>IF24FEBRUARI2027</t>
+          <t>NR26NOVEMBER2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>IF25FEBRUARI2027</t>
+          <t>NR27NOVEMBER2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>IF26FEBRUARI2027</t>
+          <t>NR28NOVEMBER2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>IF27FEBRUARI2027</t>
+          <t>NR29NOVEMBER2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>IF28FEBRUARI2027</t>
+          <t>NR30NOVEMBER2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8621,16 +8621,16 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>.github/workflows/raw-urls.yml</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>851</v>
+        <v>2168</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -8639,23 +8639,23 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/.github/workflows/raw-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>OR01OKTOBER2027</t>
+          <t>data/phxnkhlay_all_raw.csv</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>872156</v>
+        <v>46466</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -8664,23 +8664,23 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.csv</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>OR02OKTOBER2027</t>
+          <t>data/phxnkhlay_all_raw.xlsx</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>872156</v>
+        <v>16317</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -8689,23 +8689,23 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.xlsx</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>OR03OKTOBER2027</t>
+          <t>data/uppermoon77_all_raw.csv</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>872156</v>
+        <v>42049</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -8714,23 +8714,23 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.csv</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>OR04OKTOBER2027</t>
+          <t>data/uppermoon77_all_raw.xlsx</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>872156</v>
+        <v>15157</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -8739,23 +8739,23 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.xlsx</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>OR05OKTOBER2027</t>
+          <t>generate_all_repos_raw_urls.py</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>872156</v>
+        <v>6525</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/generate_all_repos_raw_urls.py</t>
         </is>
       </c>
     </row>
@@ -8776,11 +8776,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>OR06OKTOBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>872156</v>
+        <v>851</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>OR07OKTOBER2027</t>
+          <t>OR01OKTOBER2027</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>OR08OKTOBER2027</t>
+          <t>OR02OKTOBER2027</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>OR09OKTOBER2027</t>
+          <t>OR03OKTOBER2027</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>OR10OKTOBER2027</t>
+          <t>OR04OKTOBER2027</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>OR11OKTOBER2027</t>
+          <t>OR05OKTOBER2027</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>OR12OKTOBER2027</t>
+          <t>OR06OKTOBER2027</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>OR13OKTOBER2027</t>
+          <t>OR07OKTOBER2027</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>OR14OKTOBER2027</t>
+          <t>OR08OKTOBER2027</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>OR15OKTOBER2027</t>
+          <t>OR09OKTOBER2027</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>OR16OKTOBER2027</t>
+          <t>OR10OKTOBER2027</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>OR17OKTOBER2027</t>
+          <t>OR11OKTOBER2027</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>OR18OKTOBER2027</t>
+          <t>OR12OKTOBER2027</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>OR19OKTOBER2027</t>
+          <t>OR13OKTOBER2027</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>OR20OKTOBER2027</t>
+          <t>OR14OKTOBER2027</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>OR21OKTOBER2027</t>
+          <t>OR15OKTOBER2027</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>OR22OKTOBER2027</t>
+          <t>OR16OKTOBER2027</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>OR23OKTOBER2027</t>
+          <t>OR17OKTOBER2027</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>OR24OKTOBER2027</t>
+          <t>OR18OKTOBER2027</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>OR25OKTOBER2027</t>
+          <t>OR19OKTOBER2027</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>OR26OKTOBER2027</t>
+          <t>OR20OKTOBER2027</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>OR27OKTOBER2027</t>
+          <t>OR21OKTOBER2027</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>OR28OKTOBER2027</t>
+          <t>OR22OKTOBER2027</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>OR29OKTOBER2027</t>
+          <t>OR23OKTOBER2027</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>OR30OKTOBER2027</t>
+          <t>OR24OKTOBER2027</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>OR31OKTOBER2027</t>
+          <t>OR25OKTOBER2027</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
         </is>
       </c>
     </row>
@@ -9426,11 +9426,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>OR26OKTOBER2027</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>14662</v>
+        <v>872156</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -9439,23 +9439,23 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>.github/workflows/raw-urls.yml</t>
+          <t>OR27OKTOBER2027</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>2168</v>
+        <v>872156</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -9464,23 +9464,23 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/.github/workflows/raw-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>data/phxnkhlay_all_raw.csv</t>
+          <t>OR28OKTOBER2027</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>46466</v>
+        <v>872156</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -9489,23 +9489,23 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>data/phxnkhlay_all_raw.xlsx</t>
+          <t>OR29OKTOBER2027</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>16278</v>
+        <v>872156</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -9514,23 +9514,23 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.xlsx</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>data/uppermoon77_all_raw.csv</t>
+          <t>OR30OKTOBER2027</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>42049</v>
+        <v>872156</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -9539,23 +9539,23 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>data/uppermoon77_all_raw.xlsx</t>
+          <t>OR31OKTOBER2027</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>15157</v>
+        <v>872156</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -9564,23 +9564,23 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.xlsx</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>generate_all_repos_raw_urls.py</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>6525</v>
+        <v>14662</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/generate_all_repos_raw_urls.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
         </is>
       </c>
     </row>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JL01JULI2027</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JL02JULI2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JL03JULI2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JL04JULI2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JL05JULI2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -589,23 +589,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JL06JULI2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -614,23 +614,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JL07JULI2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -639,23 +639,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JL08JULI2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JL09JULI2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -689,23 +689,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JL10JULI2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JL11JULI2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -739,23 +739,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JL12JULI2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -764,23 +764,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JL13JULI2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JL14JULI2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -814,23 +814,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JL15JULI2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -839,23 +839,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JL16JULI2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -864,23 +864,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JL17JULI2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -889,23 +889,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JL18JULI2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -914,23 +914,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JL19JULI2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JL20JULI2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JL21JULI2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JL22JULI2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1014,23 +1014,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JL23JULI2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1039,23 +1039,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JL24JULI2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1064,23 +1064,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JL25JULI2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1089,23 +1089,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JL26JULI2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1114,23 +1114,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JL27JULI2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1139,23 +1139,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JL28JULI2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JL29JULI2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1189,23 +1189,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JL30JULI2027</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1214,23 +1214,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JL31JULI2027</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1239,14 +1239,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14656</v>
+        <v>14662</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>JL01JULI2027</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>JL02JULI2027</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>JL03JULI2027</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>JL04JULI2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>JL05JULI2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>JL06JULI2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>JL07JULI2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>JL08JULI2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>JL09JULI2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>JL10JULI2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>JL11JULI2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>JL12JULI2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>JL13JULI2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>JL14JULI2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>JL15JULI2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>JL16JULI2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>JL17JULI2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>JL18JULI2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>JL19JULI2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>JL20JULI2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>JL21JULI2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>JL22JULI2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>JL23JULI2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>JL24JULI2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>JL25JULI2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>JL26JULI2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>JL27JULI2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>JL28JULI2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>JL29JULI2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>JL30JULI2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>JL31JULI2027</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,14 +2064,14 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14664</v>
+        <v>14656</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,14 +2089,14 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>872156</v>
+        <v>872158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>872156</v>
+        <v>14666</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>14662</v>
+        <v>851</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1834</v>
+        <v>872157</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,23 +2939,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>13580</v>
+        <v>872157</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,23 +2964,23 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3878</v>
+        <v>872157</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>851</v>
+        <v>872157</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3039,23 +3039,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3064,23 +3064,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3114,23 +3114,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3139,23 +3139,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3164,23 +3164,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3289,23 +3289,23 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3314,23 +3314,23 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3364,23 +3364,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3389,23 +3389,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3414,23 +3414,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3439,23 +3439,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3489,23 +3489,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3539,23 +3539,23 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3614,23 +3614,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3639,23 +3639,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3664,23 +3664,23 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>872152</v>
+        <v>14664</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>872152</v>
+        <v>1834</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>872152</v>
+        <v>13580</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>872152</v>
+        <v>3878</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>14654</v>
+        <v>851</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>851</v>
+        <v>872154</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>IF01FEBRUARI2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IF02FEBRUARI2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IF03FEBRUARI2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IF04FEBRUARI2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IF05FEBRUARI2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IF06FEBRUARI2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IF07FEBRUARI2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IF08FEBRUARI2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IF09FEBRUARI2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IF10FEBRUARI2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IF11FEBRUARI2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IF12FEBRUARI2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IF13FEBRUARI2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>IF14FEBRUARI2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IF15FEBRUARI2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IF16FEBRUARI2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>IF17FEBRUARI2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IF18FEBRUARI2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IF19FEBRUARI2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IF20FEBRUARI2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IF21FEBRUARI2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IF22FEBRUARI2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IF23FEBRUARI2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>IF24FEBRUARI2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IF25FEBRUARI2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>IF26FEBRUARI2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>IF27FEBRUARI2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>IF28FEBRUARI2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>872157</v>
+        <v>872154</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>14664</v>
+        <v>872154</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,23 +4564,23 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>851</v>
+        <v>872154</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,23 +4589,23 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>872158</v>
+        <v>14658</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4614,23 +4614,23 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>872158</v>
+        <v>851</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4639,23 +4639,23 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4664,23 +4664,23 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4689,23 +4689,23 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4739,23 +4739,23 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4764,23 +4764,23 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4789,23 +4789,23 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -4814,23 +4814,23 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4839,23 +4839,23 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4864,23 +4864,23 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -4889,23 +4889,23 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4914,23 +4914,23 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4939,23 +4939,23 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -4989,23 +4989,23 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5014,23 +5014,23 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5039,23 +5039,23 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5064,23 +5064,23 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -5114,23 +5114,23 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -5139,23 +5139,23 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -5164,23 +5164,23 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -5189,23 +5189,23 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -5214,23 +5214,23 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -5239,23 +5239,23 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -5264,23 +5264,23 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,23 +5314,23 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>872158</v>
+        <v>872152</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5339,23 +5339,23 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>14666</v>
+        <v>872152</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>851</v>
+        <v>872152</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>872154</v>
+        <v>14654</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>872154</v>
+        <v>851</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,23 +6139,23 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>872154</v>
+        <v>872153</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,23 +6164,23 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>14658</v>
+        <v>872153</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
@@ -6201,11 +6201,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>851</v>
+        <v>872153</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
@@ -6226,11 +6226,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>872153</v>
+        <v>14656</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6239,23 +6239,23 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>872153</v>
+        <v>851</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6264,23 +6264,23 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6289,23 +6289,23 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6314,23 +6314,23 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6339,23 +6339,23 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6389,23 +6389,23 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6414,23 +6414,23 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -6514,23 +6514,23 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -6539,23 +6539,23 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -6564,23 +6564,23 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -6614,23 +6614,23 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -6664,23 +6664,23 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -6689,23 +6689,23 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -6764,23 +6764,23 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -6789,23 +6789,23 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -6814,23 +6814,23 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -6839,23 +6839,23 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -6864,23 +6864,23 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -6889,23 +6889,23 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -6914,23 +6914,23 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -6939,23 +6939,23 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -6964,14 +6964,14 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>14656</v>
+        <v>14664</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16317</v>
+        <v>16346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -1271,16 +1271,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>851</v>
+        <v>1834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JL01JULI2027</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>872153</v>
+        <v>13580</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JL02JULI2027</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>872153</v>
+        <v>3878</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JL03JULI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>872153</v>
+        <v>851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,19 +1364,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JL04JULI2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JL05JULI2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1414,19 +1414,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JL06JULI2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1439,19 +1439,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JL07JULI2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1464,19 +1464,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JL08JULI2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1489,19 +1489,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JL09JULI2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1514,19 +1514,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JL10JULI2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1539,19 +1539,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JL11JULI2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1564,19 +1564,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JL12JULI2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1589,19 +1589,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JL13JULI2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1614,19 +1614,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JL14JULI2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JL15JULI2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1664,19 +1664,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JL16JULI2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1689,19 +1689,19 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JL17JULI2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JL18JULI2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1739,19 +1739,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JL19JULI2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1764,19 +1764,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JL20JULI2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1789,19 +1789,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JL21JULI2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1814,19 +1814,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JL22JULI2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1839,19 +1839,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JL23JULI2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JL24JULI2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1889,19 +1889,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JL25JULI2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1914,19 +1914,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JL26JULI2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1939,19 +1939,19 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JL27JULI2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1964,19 +1964,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JL28JULI2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1989,19 +1989,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JL29JULI2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2014,19 +2014,19 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JL30JULI2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JL31JULI2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14656</v>
+        <v>872153</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>851</v>
+        <v>872153</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>872158</v>
+        <v>14656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>872158</v>
+        <v>851</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>JL01JULI2027</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>JL02JULI2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>JL03JULI2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>JL04JULI2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>JL05JULI2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>JL06JULI2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>JL07JULI2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>JL08JULI2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>JL09JULI2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>JL10JULI2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>JL11JULI2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>JL12JULI2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>JL13JULI2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>JL14JULI2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>JL15JULI2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>JL16JULI2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>JL17JULI2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>JL18JULI2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>JL19JULI2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>JL20JULI2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>JL21JULI2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>JL22JULI2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>JL23JULI2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>JL24JULI2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>JL25JULI2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>JL26JULI2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>JL27JULI2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>JL28JULI2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>JL29JULI2027</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>14666</v>
+        <v>872153</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>JL30JULI2027</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>851</v>
+        <v>872153</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>JL31JULI2027</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,23 +2939,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>872157</v>
+        <v>14656</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -2976,11 +2976,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>872157</v>
+        <v>851</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
@@ -3701,11 +3701,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>14664</v>
+        <v>872157</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1834</v>
+        <v>872157</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>13580</v>
+        <v>872157</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3878</v>
+        <v>14664</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,14 +3789,14 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>872154</v>
+        <v>872158</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,23 +4564,23 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>872154</v>
+        <v>14666</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,23 +4589,23 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>14658</v>
+        <v>851</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4614,23 +4614,23 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>851</v>
+        <v>872157</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4639,23 +4639,23 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4664,23 +4664,23 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4689,23 +4689,23 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4739,23 +4739,23 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4764,23 +4764,23 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4789,23 +4789,23 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -4814,23 +4814,23 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4839,23 +4839,23 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4864,23 +4864,23 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -4889,23 +4889,23 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4914,23 +4914,23 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4939,23 +4939,23 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -4989,23 +4989,23 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5014,23 +5014,23 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5039,23 +5039,23 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5064,23 +5064,23 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -5114,23 +5114,23 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -5139,23 +5139,23 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -5164,23 +5164,23 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -5189,23 +5189,23 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -5214,23 +5214,23 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -5239,23 +5239,23 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -5264,23 +5264,23 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>872152</v>
+        <v>872157</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,23 +5314,23 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>872152</v>
+        <v>14664</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5339,23 +5339,23 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>872152</v>
+        <v>851</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>14654</v>
+        <v>872154</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>851</v>
+        <v>872154</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,23 +6139,23 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>872153</v>
+        <v>14658</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,23 +6164,23 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>872153</v>
+        <v>851</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6189,23 +6189,23 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>NR01NOVEMBER2027</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>872153</v>
+        <v>584855</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6214,23 +6214,23 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>NR02NOVEMBER2027</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>14656</v>
+        <v>584855</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6239,23 +6239,23 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>NR03NOVEMBER2027</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>851</v>
+        <v>584855</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6264,23 +6264,23 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>IF01FEBRUARI2027</t>
+          <t>NR04NOVEMBER2027</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6289,23 +6289,23 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>IF02FEBRUARI2027</t>
+          <t>NR05NOVEMBER2027</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6314,23 +6314,23 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>IF03FEBRUARI2027</t>
+          <t>NR06NOVEMBER2027</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6339,23 +6339,23 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>IF04FEBRUARI2027</t>
+          <t>NR07NOVEMBER2027</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>IF05FEBRUARI2027</t>
+          <t>NR08NOVEMBER2027</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6389,23 +6389,23 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>IF06FEBRUARI2027</t>
+          <t>NR09NOVEMBER2027</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6414,23 +6414,23 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>IF07FEBRUARI2027</t>
+          <t>NR10NOVEMBER2027</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>IF08FEBRUARI2027</t>
+          <t>NR11NOVEMBER2027</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>IF09FEBRUARI2027</t>
+          <t>NR12NOVEMBER2027</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>IF10FEBRUARI2027</t>
+          <t>NR13NOVEMBER2027</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -6514,23 +6514,23 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>IF11FEBRUARI2027</t>
+          <t>NR14NOVEMBER2027</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -6539,23 +6539,23 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>IF12FEBRUARI2027</t>
+          <t>NR15NOVEMBER2027</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -6564,23 +6564,23 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>IF13FEBRUARI2027</t>
+          <t>NR16NOVEMBER2027</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>IF14FEBRUARI2027</t>
+          <t>NR17NOVEMBER2027</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -6614,23 +6614,23 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>IF15FEBRUARI2027</t>
+          <t>NR18NOVEMBER2027</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>IF16FEBRUARI2027</t>
+          <t>NR19NOVEMBER2027</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -6664,23 +6664,23 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IF17FEBRUARI2027</t>
+          <t>NR20NOVEMBER2027</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -6689,23 +6689,23 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>IF18FEBRUARI2027</t>
+          <t>NR21NOVEMBER2027</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>IF19FEBRUARI2027</t>
+          <t>NR22NOVEMBER2027</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>IF20FEBRUARI2027</t>
+          <t>NR23NOVEMBER2027</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -6764,23 +6764,23 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>IF21FEBRUARI2027</t>
+          <t>NR24NOVEMBER2027</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -6789,23 +6789,23 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>IF22FEBRUARI2027</t>
+          <t>NR25NOVEMBER2027</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -6814,23 +6814,23 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>IF23FEBRUARI2027</t>
+          <t>NR26NOVEMBER2027</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -6839,23 +6839,23 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IF24FEBRUARI2027</t>
+          <t>NR27NOVEMBER2027</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -6864,23 +6864,23 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>IF25FEBRUARI2027</t>
+          <t>NR28NOVEMBER2027</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -6889,23 +6889,23 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>IF26FEBRUARI2027</t>
+          <t>NR29NOVEMBER2027</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -6914,23 +6914,23 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IF27FEBRUARI2027</t>
+          <t>NR30NOVEMBER2027</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>872157</v>
+        <v>584855</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -6939,23 +6939,23 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IF28FEBRUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>872157</v>
+        <v>14664</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -6964,23 +6964,23 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>14664</v>
+        <v>851</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -6989,23 +6989,23 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>851</v>
+        <v>872152</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,23 +7014,23 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>NR01NOVEMBER2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>NR02NOVEMBER2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>NR03NOVEMBER2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>NR04NOVEMBER2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>NR05NOVEMBER2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>NR06NOVEMBER2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>NR07NOVEMBER2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>NR08NOVEMBER2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>NR09NOVEMBER2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>NR10NOVEMBER2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>NR11NOVEMBER2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>NR12NOVEMBER2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>NR13NOVEMBER2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>NR14NOVEMBER2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>NR15NOVEMBER2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>NR16NOVEMBER2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>NR17NOVEMBER2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>NR18NOVEMBER2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>NR19NOVEMBER2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>NR20NOVEMBER2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>NR21NOVEMBER2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>NR22NOVEMBER2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>NR23NOVEMBER2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>NR24NOVEMBER2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>NR25NOVEMBER2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>NR26NOVEMBER2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>NR27NOVEMBER2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>NR28NOVEMBER2027</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>NR29NOVEMBER2027</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>NR30NOVEMBER2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>14664</v>
+        <v>14654</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,14 +7789,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7814,23 +7814,23 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>MT01MARET2027</t>
+          <t>OR01OKTOBER2027</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -7839,23 +7839,23 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MT02MARET2027</t>
+          <t>OR02OKTOBER2027</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -7864,23 +7864,23 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MT03MARET2027</t>
+          <t>OR03OKTOBER2027</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -7889,23 +7889,23 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>MT04MARET2027</t>
+          <t>OR04OKTOBER2027</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -7914,23 +7914,23 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MT05MARET2027</t>
+          <t>OR05OKTOBER2027</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -7939,23 +7939,23 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>MT06MARET2027</t>
+          <t>OR06OKTOBER2027</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -7964,23 +7964,23 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MT07MARET2027</t>
+          <t>OR07OKTOBER2027</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -7989,23 +7989,23 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MT08MARET2027</t>
+          <t>OR08OKTOBER2027</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -8014,23 +8014,23 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MT09MARET2027</t>
+          <t>OR09OKTOBER2027</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -8039,23 +8039,23 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MT10MARET2027</t>
+          <t>OR10OKTOBER2027</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -8064,23 +8064,23 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>MT11MARET2027</t>
+          <t>OR11OKTOBER2027</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -8089,23 +8089,23 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>MT12MARET2027</t>
+          <t>OR12OKTOBER2027</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -8114,23 +8114,23 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>MT13MARET2027</t>
+          <t>OR13OKTOBER2027</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -8139,23 +8139,23 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>MT14MARET2027</t>
+          <t>OR14OKTOBER2027</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -8164,23 +8164,23 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>MT15MARET2027</t>
+          <t>OR15OKTOBER2027</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -8189,23 +8189,23 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MT16MARET2027</t>
+          <t>OR16OKTOBER2027</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -8214,23 +8214,23 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>MT17MARET2027</t>
+          <t>OR17OKTOBER2027</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -8239,23 +8239,23 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MT18MARET2027</t>
+          <t>OR18OKTOBER2027</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -8264,23 +8264,23 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MT19MARET2027</t>
+          <t>OR19OKTOBER2027</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -8289,23 +8289,23 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>MT20MARET2027</t>
+          <t>OR20OKTOBER2027</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MT21MARET2027</t>
+          <t>OR21OKTOBER2027</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -8339,23 +8339,23 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MT22MARET2027</t>
+          <t>OR22OKTOBER2027</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -8364,23 +8364,23 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>MT23MARET2027</t>
+          <t>OR23OKTOBER2027</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -8389,23 +8389,23 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MT24MARET2027</t>
+          <t>OR24OKTOBER2027</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -8414,23 +8414,23 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>MT25MARET2027</t>
+          <t>OR25OKTOBER2027</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -8439,23 +8439,23 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>MT26MARET2027</t>
+          <t>OR26OKTOBER2027</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -8464,23 +8464,23 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>MT27MARET2027</t>
+          <t>OR27OKTOBER2027</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -8489,23 +8489,23 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>MT28MARET2027</t>
+          <t>OR28OKTOBER2027</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -8514,23 +8514,23 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>MT29MARET2027</t>
+          <t>OR29OKTOBER2027</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -8539,23 +8539,23 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>MT30MARET2027</t>
+          <t>OR30OKTOBER2027</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -8564,23 +8564,23 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>MT31MARET2027</t>
+          <t>OR31OKTOBER2027</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>14656</v>
+        <v>14662</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16346</v>
+        <v>16275</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8789,23 +8789,23 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>OR01OKTOBER2027</t>
+          <t>MT01MARET2027</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -8814,23 +8814,23 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>OR02OKTOBER2027</t>
+          <t>MT02MARET2027</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -8839,23 +8839,23 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>OR03OKTOBER2027</t>
+          <t>MT03MARET2027</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -8864,23 +8864,23 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>OR04OKTOBER2027</t>
+          <t>MT04MARET2027</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -8889,23 +8889,23 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>OR05OKTOBER2027</t>
+          <t>MT05MARET2027</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -8914,23 +8914,23 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>OR06OKTOBER2027</t>
+          <t>MT06MARET2027</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -8939,23 +8939,23 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>OR07OKTOBER2027</t>
+          <t>MT07MARET2027</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -8964,23 +8964,23 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>OR08OKTOBER2027</t>
+          <t>MT08MARET2027</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -8989,23 +8989,23 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>OR09OKTOBER2027</t>
+          <t>MT09MARET2027</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -9014,23 +9014,23 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>OR10OKTOBER2027</t>
+          <t>MT10MARET2027</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -9039,23 +9039,23 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>OR11OKTOBER2027</t>
+          <t>MT11MARET2027</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -9064,23 +9064,23 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>OR12OKTOBER2027</t>
+          <t>MT12MARET2027</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -9089,23 +9089,23 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>OR13OKTOBER2027</t>
+          <t>MT13MARET2027</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -9114,23 +9114,23 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>OR14OKTOBER2027</t>
+          <t>MT14MARET2027</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -9139,23 +9139,23 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>OR15OKTOBER2027</t>
+          <t>MT15MARET2027</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -9164,23 +9164,23 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>OR16OKTOBER2027</t>
+          <t>MT16MARET2027</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -9189,23 +9189,23 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>OR17OKTOBER2027</t>
+          <t>MT17MARET2027</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -9214,23 +9214,23 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>OR18OKTOBER2027</t>
+          <t>MT18MARET2027</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -9239,23 +9239,23 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>OR19OKTOBER2027</t>
+          <t>MT19MARET2027</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -9264,23 +9264,23 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>OR20OKTOBER2027</t>
+          <t>MT20MARET2027</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -9289,23 +9289,23 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>OR21OKTOBER2027</t>
+          <t>MT21MARET2027</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -9314,23 +9314,23 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>OR22OKTOBER2027</t>
+          <t>MT22MARET2027</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -9339,23 +9339,23 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>OR23OKTOBER2027</t>
+          <t>MT23MARET2027</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -9364,23 +9364,23 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>OR24OKTOBER2027</t>
+          <t>MT24MARET2027</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -9389,23 +9389,23 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>OR25OKTOBER2027</t>
+          <t>MT25MARET2027</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -9414,23 +9414,23 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>OR26OKTOBER2027</t>
+          <t>MT26MARET2027</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -9439,23 +9439,23 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>OR27OKTOBER2027</t>
+          <t>MT27MARET2027</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -9464,23 +9464,23 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>OR28OKTOBER2027</t>
+          <t>MT28MARET2027</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -9489,23 +9489,23 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>OR29OKTOBER2027</t>
+          <t>MT29MARET2027</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -9514,23 +9514,23 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>OR30OKTOBER2027</t>
+          <t>MT30MARET2027</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -9539,23 +9539,23 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>OR31OKTOBER2027</t>
+          <t>MT31MARET2027</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -9564,14 +9564,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>14662</v>
+        <v>14656</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
         </is>
       </c>
     </row>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>JL01JULI2027</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>JL02JULI2027</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>JL03JULI2027</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>JL04JULI2027</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>JL05JULI2027</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -589,23 +589,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>JL06JULI2027</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -614,23 +614,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>JL07JULI2027</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -639,23 +639,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>JL08JULI2027</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>JL09JULI2027</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -689,23 +689,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>JL10JULI2027</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>JL11JULI2027</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -739,23 +739,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>JL12JULI2027</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -764,23 +764,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>JL13JULI2027</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>JL14JULI2027</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -814,23 +814,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>JL15JULI2027</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -839,23 +839,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>JL16JULI2027</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -864,23 +864,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>JL17JULI2027</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -889,23 +889,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>JL18JULI2027</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -914,23 +914,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>JL19JULI2027</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>JL20JULI2027</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>JL21JULI2027</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>JL22JULI2027</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1014,23 +1014,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>JL23JULI2027</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1039,23 +1039,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>JL24JULI2027</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1064,23 +1064,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>JL25JULI2027</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1089,23 +1089,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>JL26JULI2027</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1114,23 +1114,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>JL27JULI2027</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1139,23 +1139,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>JL28JULI2027</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>JL29JULI2027</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1189,23 +1189,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>JL30JULI2027</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1214,23 +1214,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>JL31JULI2027</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>872156</v>
+        <v>872153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1239,14 +1239,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14662</v>
+        <v>14656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1264,23 +1264,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1834</v>
+        <v>851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>13580</v>
+        <v>872156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3878</v>
+        <v>872156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>851</v>
+        <v>872156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>872153</v>
+        <v>872156</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>872153</v>
+        <v>14662</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>872153</v>
+        <v>851</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>14656</v>
+        <v>872157</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>851</v>
+        <v>872157</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JL01JULI2027</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JL02JULI2027</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JL03JULI2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JL04JULI2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JL05JULI2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JL06JULI2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JL07JULI2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JL08JULI2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JL09JULI2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JL10JULI2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JL11JULI2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JL12JULI2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JL13JULI2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JL14JULI2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JL15JULI2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JL16JULI2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JL17JULI2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JL18JULI2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JL19JULI2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JL20JULI2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JL21JULI2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JL22JULI2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JL23JULI2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JL24JULI2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JL25JULI2027</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JL26JULI2027</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JL27JULI2027</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JL28JULI2027</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JL29JULI2027</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>872153</v>
+        <v>872157</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JL30JULI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>872153</v>
+        <v>14664</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JL31JULI2027</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>872153</v>
+        <v>1834</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,23 +2939,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>14656</v>
+        <v>13580</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,23 +2964,23 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>851</v>
+        <v>3878</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>872157</v>
+        <v>851</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3039,23 +3039,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3064,23 +3064,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3114,23 +3114,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3139,23 +3139,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3164,23 +3164,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3289,23 +3289,23 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3314,23 +3314,23 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3364,23 +3364,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3389,23 +3389,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3414,23 +3414,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3439,23 +3439,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3489,23 +3489,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3539,23 +3539,23 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3614,23 +3614,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3639,23 +3639,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3664,23 +3664,23 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>872157</v>
+        <v>872158</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,14 +3764,14 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>14664</v>
+        <v>14666</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,14 +3789,14 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>872158</v>
+        <v>872153</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,14 +4564,14 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>14666</v>
+        <v>14656</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>872154</v>
+        <v>872152</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,14 +6139,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>14658</v>
+        <v>14654</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6989,23 +6989,23 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,23 +7014,23 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>872152</v>
+        <v>872154</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>14654</v>
+        <v>14658</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,14 +7789,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7814,23 +7814,23 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>OR01OKTOBER2027</t>
+          <t>MT01MARET2027</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -7839,23 +7839,23 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>OR02OKTOBER2027</t>
+          <t>MT02MARET2027</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -7864,23 +7864,23 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>OR03OKTOBER2027</t>
+          <t>MT03MARET2027</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -7889,23 +7889,23 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>OR04OKTOBER2027</t>
+          <t>MT04MARET2027</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -7914,23 +7914,23 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>OR05OKTOBER2027</t>
+          <t>MT05MARET2027</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -7939,23 +7939,23 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>OR06OKTOBER2027</t>
+          <t>MT06MARET2027</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -7964,23 +7964,23 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>OR07OKTOBER2027</t>
+          <t>MT07MARET2027</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -7989,23 +7989,23 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>OR08OKTOBER2027</t>
+          <t>MT08MARET2027</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -8014,23 +8014,23 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>OR09OKTOBER2027</t>
+          <t>MT09MARET2027</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -8039,23 +8039,23 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>OR10OKTOBER2027</t>
+          <t>MT10MARET2027</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -8064,23 +8064,23 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>OR11OKTOBER2027</t>
+          <t>MT11MARET2027</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -8089,23 +8089,23 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>OR12OKTOBER2027</t>
+          <t>MT12MARET2027</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -8114,23 +8114,23 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>OR13OKTOBER2027</t>
+          <t>MT13MARET2027</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -8139,23 +8139,23 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>OR14OKTOBER2027</t>
+          <t>MT14MARET2027</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -8164,23 +8164,23 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>OR15OKTOBER2027</t>
+          <t>MT15MARET2027</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -8189,23 +8189,23 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>OR16OKTOBER2027</t>
+          <t>MT16MARET2027</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -8214,23 +8214,23 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>OR17OKTOBER2027</t>
+          <t>MT17MARET2027</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -8239,23 +8239,23 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>OR18OKTOBER2027</t>
+          <t>MT18MARET2027</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -8264,23 +8264,23 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>OR19OKTOBER2027</t>
+          <t>MT19MARET2027</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -8289,23 +8289,23 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>OR20OKTOBER2027</t>
+          <t>MT20MARET2027</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>OR21OKTOBER2027</t>
+          <t>MT21MARET2027</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -8339,23 +8339,23 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>OR22OKTOBER2027</t>
+          <t>MT22MARET2027</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -8364,23 +8364,23 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>OR23OKTOBER2027</t>
+          <t>MT23MARET2027</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -8389,23 +8389,23 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>OR24OKTOBER2027</t>
+          <t>MT24MARET2027</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -8414,23 +8414,23 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>OR25OKTOBER2027</t>
+          <t>MT25MARET2027</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -8439,23 +8439,23 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>OR26OKTOBER2027</t>
+          <t>MT26MARET2027</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -8464,23 +8464,23 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>OR27OKTOBER2027</t>
+          <t>MT27MARET2027</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -8489,23 +8489,23 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>OR28OKTOBER2027</t>
+          <t>MT28MARET2027</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -8514,23 +8514,23 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>OR29OKTOBER2027</t>
+          <t>MT29MARET2027</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -8539,23 +8539,23 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>OR30OKTOBER2027</t>
+          <t>MT30MARET2027</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -8564,23 +8564,23 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>OR31OKTOBER2027</t>
+          <t>MT31MARET2027</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>872156</v>
+        <v>872154</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>14662</v>
+        <v>14656</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16275</v>
+        <v>16301</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8789,23 +8789,23 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MT01MARET2027</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -8814,23 +8814,23 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MT02MARET2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -8839,23 +8839,23 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>MT03MARET2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -8864,23 +8864,23 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MT04MARET2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -8889,23 +8889,23 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MT05MARET2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -8914,23 +8914,23 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>MT06MARET2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -8939,23 +8939,23 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>MT07MARET2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -8964,23 +8964,23 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>MT08MARET2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -8989,23 +8989,23 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>MT09MARET2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -9014,23 +9014,23 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>MT10MARET2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -9039,23 +9039,23 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>MT11MARET2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -9064,23 +9064,23 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>MT12MARET2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -9089,23 +9089,23 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>MT13MARET2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -9114,23 +9114,23 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MT14MARET2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -9139,23 +9139,23 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MT15MARET2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -9164,23 +9164,23 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MT16MARET2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -9189,23 +9189,23 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MT17MARET2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -9214,23 +9214,23 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MT18MARET2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -9239,23 +9239,23 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>MT19MARET2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -9264,23 +9264,23 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>MT20MARET2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -9289,23 +9289,23 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>MT21MARET2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -9314,23 +9314,23 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MT22MARET2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -9339,23 +9339,23 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>MT23MARET2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -9364,23 +9364,23 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MT24MARET2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -9389,23 +9389,23 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>MT25MARET2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -9414,23 +9414,23 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MT26MARET2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -9439,23 +9439,23 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MT27MARET2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -9464,23 +9464,23 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MT28MARET2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -9489,23 +9489,23 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MT29MARET2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -9514,23 +9514,23 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MT30MARET2027</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -9539,23 +9539,23 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MT31MARET2027</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>872154</v>
+        <v>905893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -9564,23 +9564,23 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>SA01AGUSTUS2027</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>14656</v>
+        <v>872156</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA01AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9601,11 +9601,11 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>SA02AGUSTUS2027</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>851</v>
+        <v>872156</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA02AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9626,11 +9626,11 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>SA03AGUSTUS2027</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA03AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>SA04AGUSTUS2027</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA04AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9676,11 +9676,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>SA05AGUSTUS2027</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA05AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9701,11 +9701,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>SA06AGUSTUS2027</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA06AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9726,11 +9726,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>SA07AGUSTUS2027</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA07AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9751,11 +9751,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>SA08AGUSTUS2027</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA08AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9776,11 +9776,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>SA09AGUSTUS2027</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA09AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9801,11 +9801,11 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>SA10AGUSTUS2027</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA10AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9826,11 +9826,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>SA11AGUSTUS2027</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA11AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9851,11 +9851,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>SA12AGUSTUS2027</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA12AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9876,11 +9876,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>SA13AGUSTUS2027</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA13AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9901,11 +9901,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>SA14AGUSTUS2027</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA14AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9926,11 +9926,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>SA15AGUSTUS2027</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA15AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9951,11 +9951,11 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>SA16AGUSTUS2027</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA16AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -9976,11 +9976,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>SA17AGUSTUS2027</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA17AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10001,11 +10001,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>SA18AGUSTUS2027</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA18AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10026,11 +10026,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>SA19AGUSTUS2027</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA19AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10051,11 +10051,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>SA20AGUSTUS2027</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA20AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10076,11 +10076,11 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>SA21AGUSTUS2027</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA21AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10101,11 +10101,11 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>SA22AGUSTUS2027</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA22AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10126,11 +10126,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>SA23AGUSTUS2027</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA23AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10151,11 +10151,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>SA24AGUSTUS2027</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA24AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10176,11 +10176,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>SA25AGUSTUS2027</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA25AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10201,11 +10201,11 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>SA26AGUSTUS2027</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA26AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10226,11 +10226,11 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>SA27AGUSTUS2027</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA27AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10251,11 +10251,11 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>SA28AGUSTUS2027</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA28AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10276,11 +10276,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>SA29AGUSTUS2027</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA29AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10301,11 +10301,11 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>SA30AGUSTUS2027</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA30AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10326,11 +10326,11 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>SA31AGUSTUS2027</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>905893</v>
+        <v>872156</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA31AGUSTUS2027</t>
         </is>
       </c>
     </row>
@@ -10351,11 +10351,11 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>905893</v>
+        <v>14662</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -10364,23 +10364,23 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>905893</v>
+        <v>851</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -10389,19 +10389,19 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SA01AGUSTUS2027</t>
+          <t>OR01OKTOBER2027</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -10414,19 +10414,19 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA01AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>SA02AGUSTUS2027</t>
+          <t>OR02OKTOBER2027</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -10439,19 +10439,19 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA02AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>SA03AGUSTUS2027</t>
+          <t>OR03OKTOBER2027</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -10464,19 +10464,19 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA03AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>SA04AGUSTUS2027</t>
+          <t>OR04OKTOBER2027</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -10489,19 +10489,19 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA04AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>SA05AGUSTUS2027</t>
+          <t>OR05OKTOBER2027</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -10514,19 +10514,19 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA05AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>SA06AGUSTUS2027</t>
+          <t>OR06OKTOBER2027</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -10539,19 +10539,19 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA06AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>SA07AGUSTUS2027</t>
+          <t>OR07OKTOBER2027</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -10564,19 +10564,19 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA07AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>SA08AGUSTUS2027</t>
+          <t>OR08OKTOBER2027</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -10589,19 +10589,19 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA08AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>SA09AGUSTUS2027</t>
+          <t>OR09OKTOBER2027</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -10614,19 +10614,19 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA09AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>SA10AGUSTUS2027</t>
+          <t>OR10OKTOBER2027</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -10639,19 +10639,19 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA10AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>SA11AGUSTUS2027</t>
+          <t>OR11OKTOBER2027</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -10664,19 +10664,19 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA11AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>SA12AGUSTUS2027</t>
+          <t>OR12OKTOBER2027</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -10689,19 +10689,19 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA12AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>SA13AGUSTUS2027</t>
+          <t>OR13OKTOBER2027</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -10714,19 +10714,19 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA13AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>SA14AGUSTUS2027</t>
+          <t>OR14OKTOBER2027</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -10739,19 +10739,19 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA14AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>SA15AGUSTUS2027</t>
+          <t>OR15OKTOBER2027</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -10764,19 +10764,19 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA15AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>SA16AGUSTUS2027</t>
+          <t>OR16OKTOBER2027</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -10789,19 +10789,19 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA16AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>SA17AGUSTUS2027</t>
+          <t>OR17OKTOBER2027</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -10814,19 +10814,19 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA17AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>SA18AGUSTUS2027</t>
+          <t>OR18OKTOBER2027</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -10839,19 +10839,19 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA18AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>SA19AGUSTUS2027</t>
+          <t>OR19OKTOBER2027</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -10864,19 +10864,19 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA19AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>SA20AGUSTUS2027</t>
+          <t>OR20OKTOBER2027</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -10889,19 +10889,19 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA20AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>SA21AGUSTUS2027</t>
+          <t>OR21OKTOBER2027</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -10914,19 +10914,19 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA21AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>SA22AGUSTUS2027</t>
+          <t>OR22OKTOBER2027</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -10939,19 +10939,19 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA22AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>SA23AGUSTUS2027</t>
+          <t>OR23OKTOBER2027</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -10964,19 +10964,19 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA23AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>SA24AGUSTUS2027</t>
+          <t>OR24OKTOBER2027</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -10989,19 +10989,19 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA24AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>SA25AGUSTUS2027</t>
+          <t>OR25OKTOBER2027</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -11014,19 +11014,19 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA25AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SA26AGUSTUS2027</t>
+          <t>OR26OKTOBER2027</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -11039,19 +11039,19 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA26AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>SA27AGUSTUS2027</t>
+          <t>OR27OKTOBER2027</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -11064,19 +11064,19 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA27AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>SA28AGUSTUS2027</t>
+          <t>OR28OKTOBER2027</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -11089,19 +11089,19 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA28AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SA29AGUSTUS2027</t>
+          <t>OR29OKTOBER2027</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -11114,19 +11114,19 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA29AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>SA30AGUSTUS2027</t>
+          <t>OR30OKTOBER2027</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -11139,19 +11139,19 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA30AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>SA31AGUSTUS2027</t>
+          <t>OR31OKTOBER2027</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -11164,14 +11164,14 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA31AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
         </is>
       </c>
     </row>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -3796,7 +3796,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>872153</v>
+        <v>872154</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,23 +4564,23 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>14656</v>
+        <v>872154</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,23 +4589,23 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>851</v>
+        <v>14658</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4614,23 +4614,23 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IF01FEBRUARI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>872157</v>
+        <v>851</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4639,23 +4639,23 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IF02FEBRUARI2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4664,23 +4664,23 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IF03FEBRUARI2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4689,23 +4689,23 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IF04FEBRUARI2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IF05FEBRUARI2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4739,23 +4739,23 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IF06FEBRUARI2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4764,23 +4764,23 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IF07FEBRUARI2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4789,23 +4789,23 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IF08FEBRUARI2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -4814,23 +4814,23 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IF09FEBRUARI2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4839,23 +4839,23 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>IF10FEBRUARI2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4864,23 +4864,23 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IF11FEBRUARI2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -4889,23 +4889,23 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IF12FEBRUARI2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4914,23 +4914,23 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IF13FEBRUARI2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4939,23 +4939,23 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IF14FEBRUARI2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>IF15FEBRUARI2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -4989,23 +4989,23 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>IF16FEBRUARI2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5014,23 +5014,23 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>IF17FEBRUARI2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5039,23 +5039,23 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IF18FEBRUARI2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5064,23 +5064,23 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IF19FEBRUARI2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IF20FEBRUARI2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -5114,23 +5114,23 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IF21FEBRUARI2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -5139,23 +5139,23 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>IF22FEBRUARI2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -5164,23 +5164,23 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IF23FEBRUARI2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -5189,23 +5189,23 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>IF24FEBRUARI2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -5214,23 +5214,23 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IF25FEBRUARI2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -5239,23 +5239,23 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IF26FEBRUARI2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -5264,23 +5264,23 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IF27FEBRUARI2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>IF28FEBRUARI2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>872157</v>
+        <v>872153</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,23 +5314,23 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>14664</v>
+        <v>872153</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5339,23 +5339,23 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>851</v>
+        <v>872153</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>872152</v>
+        <v>872153</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>872152</v>
+        <v>14656</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -5426,11 +5426,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>872152</v>
+        <v>851</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
@@ -6151,11 +6151,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>14654</v>
+        <v>872152</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,23 +6164,23 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>851</v>
+        <v>872152</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6189,23 +6189,23 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>NR01NOVEMBER2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>584855</v>
+        <v>872152</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6214,23 +6214,23 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>NR02NOVEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>584855</v>
+        <v>14654</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6239,23 +6239,23 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>NR03NOVEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>584855</v>
+        <v>851</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6264,23 +6264,23 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NR04NOVEMBER2027</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6289,23 +6289,23 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>NR05NOVEMBER2027</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6314,23 +6314,23 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>NR06NOVEMBER2027</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6339,23 +6339,23 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>NR07NOVEMBER2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>NR08NOVEMBER2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6389,23 +6389,23 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>NR09NOVEMBER2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6414,23 +6414,23 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>NR10NOVEMBER2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>NR11NOVEMBER2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>NR12NOVEMBER2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>NR13NOVEMBER2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -6514,23 +6514,23 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>NR14NOVEMBER2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -6539,23 +6539,23 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>NR15NOVEMBER2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -6564,23 +6564,23 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>NR16NOVEMBER2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>NR17NOVEMBER2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -6614,23 +6614,23 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>NR18NOVEMBER2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>NR19NOVEMBER2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -6664,23 +6664,23 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>NR20NOVEMBER2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -6689,23 +6689,23 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>NR21NOVEMBER2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>NR22NOVEMBER2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>NR23NOVEMBER2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -6764,23 +6764,23 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>NR24NOVEMBER2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -6789,23 +6789,23 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>NR25NOVEMBER2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -6814,23 +6814,23 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>NR26NOVEMBER2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -6839,23 +6839,23 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>NR27NOVEMBER2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -6864,23 +6864,23 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>NR28NOVEMBER2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -6889,23 +6889,23 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>NR29NOVEMBER2027</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -6914,23 +6914,23 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>NR30NOVEMBER2027</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>584855</v>
+        <v>872157</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -6939,23 +6939,23 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>14664</v>
+        <v>872157</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -6964,23 +6964,23 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>851</v>
+        <v>14664</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -6989,23 +6989,23 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>872154</v>
+        <v>851</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,23 +7014,23 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>NR01NOVEMBER2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>NR02NOVEMBER2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>NR03NOVEMBER2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>NR04NOVEMBER2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>NR05NOVEMBER2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>NR06NOVEMBER2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>NR07NOVEMBER2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>NR08NOVEMBER2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>NR09NOVEMBER2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>NR10NOVEMBER2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>NR11NOVEMBER2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>NR12NOVEMBER2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>NR13NOVEMBER2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>NR14NOVEMBER2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>NR15NOVEMBER2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>NR16NOVEMBER2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>NR17NOVEMBER2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>NR18NOVEMBER2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>NR19NOVEMBER2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>NR20NOVEMBER2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>NR21NOVEMBER2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>NR22NOVEMBER2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>NR23NOVEMBER2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>NR24NOVEMBER2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>NR25NOVEMBER2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>NR26NOVEMBER2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>NR27NOVEMBER2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>NR28NOVEMBER2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>NR29NOVEMBER2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>NR30NOVEMBER2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>872154</v>
+        <v>584855</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>14658</v>
+        <v>14664</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,14 +7789,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7814,23 +7814,23 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>MT01MARET2027</t>
+          <t>OR01OKTOBER2027</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -7839,23 +7839,23 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MT02MARET2027</t>
+          <t>OR02OKTOBER2027</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -7864,23 +7864,23 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MT03MARET2027</t>
+          <t>OR03OKTOBER2027</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -7889,23 +7889,23 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>MT04MARET2027</t>
+          <t>OR04OKTOBER2027</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -7914,23 +7914,23 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MT05MARET2027</t>
+          <t>OR05OKTOBER2027</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -7939,23 +7939,23 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>MT06MARET2027</t>
+          <t>OR06OKTOBER2027</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -7964,23 +7964,23 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MT07MARET2027</t>
+          <t>OR07OKTOBER2027</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -7989,23 +7989,23 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MT08MARET2027</t>
+          <t>OR08OKTOBER2027</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -8014,23 +8014,23 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MT09MARET2027</t>
+          <t>OR09OKTOBER2027</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -8039,23 +8039,23 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MT10MARET2027</t>
+          <t>OR10OKTOBER2027</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -8064,23 +8064,23 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>MT11MARET2027</t>
+          <t>OR11OKTOBER2027</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -8089,23 +8089,23 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>MT12MARET2027</t>
+          <t>OR12OKTOBER2027</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -8114,23 +8114,23 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>MT13MARET2027</t>
+          <t>OR13OKTOBER2027</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -8139,23 +8139,23 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>MT14MARET2027</t>
+          <t>OR14OKTOBER2027</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -8164,23 +8164,23 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>MT15MARET2027</t>
+          <t>OR15OKTOBER2027</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -8189,23 +8189,23 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MT16MARET2027</t>
+          <t>OR16OKTOBER2027</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -8214,23 +8214,23 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>MT17MARET2027</t>
+          <t>OR17OKTOBER2027</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -8239,23 +8239,23 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MT18MARET2027</t>
+          <t>OR18OKTOBER2027</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -8264,23 +8264,23 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MT19MARET2027</t>
+          <t>OR19OKTOBER2027</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -8289,23 +8289,23 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>MT20MARET2027</t>
+          <t>OR20OKTOBER2027</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MT21MARET2027</t>
+          <t>OR21OKTOBER2027</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -8339,23 +8339,23 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MT22MARET2027</t>
+          <t>OR22OKTOBER2027</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -8364,23 +8364,23 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>MT23MARET2027</t>
+          <t>OR23OKTOBER2027</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -8389,23 +8389,23 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MT24MARET2027</t>
+          <t>OR24OKTOBER2027</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -8414,23 +8414,23 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>MT25MARET2027</t>
+          <t>OR25OKTOBER2027</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -8439,23 +8439,23 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>MT26MARET2027</t>
+          <t>OR26OKTOBER2027</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -8464,23 +8464,23 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>MT27MARET2027</t>
+          <t>OR27OKTOBER2027</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -8489,23 +8489,23 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>MT28MARET2027</t>
+          <t>OR28OKTOBER2027</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -8514,23 +8514,23 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>MT29MARET2027</t>
+          <t>OR29OKTOBER2027</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -8539,23 +8539,23 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>MT30MARET2027</t>
+          <t>OR30OKTOBER2027</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -8564,23 +8564,23 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>MT31MARET2027</t>
+          <t>OR31OKTOBER2027</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>872154</v>
+        <v>872156</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>14656</v>
+        <v>14662</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16301</v>
+        <v>16306</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8789,23 +8789,23 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>MT01MARET2027</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -8814,23 +8814,23 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>MT02MARET2027</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -8839,23 +8839,23 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>MT03MARET2027</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -8864,23 +8864,23 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>MT04MARET2027</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -8889,23 +8889,23 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>MT05MARET2027</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -8914,23 +8914,23 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>MT06MARET2027</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -8939,23 +8939,23 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>MT07MARET2027</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -8964,23 +8964,23 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>MT08MARET2027</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -8989,23 +8989,23 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>MT09MARET2027</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -9014,23 +9014,23 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>MT10MARET2027</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -9039,23 +9039,23 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>MT11MARET2027</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -9064,23 +9064,23 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>MT12MARET2027</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -9089,23 +9089,23 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>MT13MARET2027</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -9114,23 +9114,23 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>MT14MARET2027</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -9139,23 +9139,23 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>MT15MARET2027</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -9164,23 +9164,23 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>MT16MARET2027</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -9189,23 +9189,23 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>MT17MARET2027</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -9214,23 +9214,23 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>MT18MARET2027</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -9239,23 +9239,23 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>MT19MARET2027</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -9264,23 +9264,23 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>MT20MARET2027</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -9289,23 +9289,23 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>MT21MARET2027</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -9314,23 +9314,23 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>MT22MARET2027</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -9339,23 +9339,23 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>MT23MARET2027</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -9364,23 +9364,23 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>MT24MARET2027</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -9389,23 +9389,23 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>MT25MARET2027</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -9414,23 +9414,23 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>MT26MARET2027</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -9439,23 +9439,23 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>MT27MARET2027</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -9464,23 +9464,23 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>MT28MARET2027</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -9489,23 +9489,23 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>MT29MARET2027</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -9514,23 +9514,23 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>MT30MARET2027</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -9539,23 +9539,23 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>MT31MARET2027</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>905893</v>
+        <v>872154</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -9564,23 +9564,23 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>sutsugA</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>SA01AGUSTUS2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>872156</v>
+        <v>14656</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA01AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -9601,11 +9601,11 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SA02AGUSTUS2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>872156</v>
+        <v>851</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA02AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -9626,11 +9626,11 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>SA03AGUSTUS2027</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA03AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SA04AGUSTUS2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA04AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9676,11 +9676,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SA05AGUSTUS2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA05AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9701,11 +9701,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SA06AGUSTUS2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA06AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9726,11 +9726,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>SA07AGUSTUS2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA07AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9751,11 +9751,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>SA08AGUSTUS2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA08AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9776,11 +9776,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>SA09AGUSTUS2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA09AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9801,11 +9801,11 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>SA10AGUSTUS2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA10AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9826,11 +9826,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>SA11AGUSTUS2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA11AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9851,11 +9851,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>SA12AGUSTUS2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA12AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9876,11 +9876,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SA13AGUSTUS2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA13AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9901,11 +9901,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SA14AGUSTUS2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA14AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9926,11 +9926,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>SA15AGUSTUS2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA15AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9951,11 +9951,11 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>SA16AGUSTUS2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA16AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -9976,11 +9976,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SA17AGUSTUS2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA17AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10001,11 +10001,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SA18AGUSTUS2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA18AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10026,11 +10026,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SA19AGUSTUS2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA19AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10051,11 +10051,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>SA20AGUSTUS2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA20AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10076,11 +10076,11 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>SA21AGUSTUS2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA21AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10101,11 +10101,11 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SA22AGUSTUS2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA22AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10126,11 +10126,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>SA23AGUSTUS2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA23AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10151,11 +10151,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SA24AGUSTUS2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA24AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10176,11 +10176,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>SA25AGUSTUS2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA25AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10201,11 +10201,11 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>SA26AGUSTUS2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA26AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10226,11 +10226,11 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>SA27AGUSTUS2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA27AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10251,11 +10251,11 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>SA28AGUSTUS2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA28AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10276,11 +10276,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>SA29AGUSTUS2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA29AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10301,11 +10301,11 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SA30AGUSTUS2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA30AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10326,11 +10326,11 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>SA31AGUSTUS2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>872156</v>
+        <v>905893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA31AGUSTUS2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
@@ -10351,11 +10351,11 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>14662</v>
+        <v>905893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -10364,23 +10364,23 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>851</v>
+        <v>905893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -10389,19 +10389,19 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>OR01OKTOBER2027</t>
+          <t>SA01AGUSTUS2027</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -10414,19 +10414,19 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA01AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>OR02OKTOBER2027</t>
+          <t>SA02AGUSTUS2027</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -10439,19 +10439,19 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA02AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>OR03OKTOBER2027</t>
+          <t>SA03AGUSTUS2027</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -10464,19 +10464,19 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA03AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>OR04OKTOBER2027</t>
+          <t>SA04AGUSTUS2027</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -10489,19 +10489,19 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA04AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>OR05OKTOBER2027</t>
+          <t>SA05AGUSTUS2027</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -10514,19 +10514,19 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA05AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>OR06OKTOBER2027</t>
+          <t>SA06AGUSTUS2027</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -10539,19 +10539,19 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA06AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>OR07OKTOBER2027</t>
+          <t>SA07AGUSTUS2027</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -10564,19 +10564,19 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA07AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>OR08OKTOBER2027</t>
+          <t>SA08AGUSTUS2027</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -10589,19 +10589,19 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA08AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>OR09OKTOBER2027</t>
+          <t>SA09AGUSTUS2027</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -10614,19 +10614,19 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA09AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>OR10OKTOBER2027</t>
+          <t>SA10AGUSTUS2027</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -10639,19 +10639,19 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA10AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>OR11OKTOBER2027</t>
+          <t>SA11AGUSTUS2027</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -10664,19 +10664,19 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA11AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>OR12OKTOBER2027</t>
+          <t>SA12AGUSTUS2027</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -10689,19 +10689,19 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA12AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>OR13OKTOBER2027</t>
+          <t>SA13AGUSTUS2027</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -10714,19 +10714,19 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA13AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>OR14OKTOBER2027</t>
+          <t>SA14AGUSTUS2027</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -10739,19 +10739,19 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA14AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>OR15OKTOBER2027</t>
+          <t>SA15AGUSTUS2027</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -10764,19 +10764,19 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA15AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>OR16OKTOBER2027</t>
+          <t>SA16AGUSTUS2027</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -10789,19 +10789,19 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA16AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>OR17OKTOBER2027</t>
+          <t>SA17AGUSTUS2027</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -10814,19 +10814,19 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA17AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>OR18OKTOBER2027</t>
+          <t>SA18AGUSTUS2027</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -10839,19 +10839,19 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA18AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>OR19OKTOBER2027</t>
+          <t>SA19AGUSTUS2027</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -10864,19 +10864,19 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA19AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>OR20OKTOBER2027</t>
+          <t>SA20AGUSTUS2027</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -10889,19 +10889,19 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA20AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>OR21OKTOBER2027</t>
+          <t>SA21AGUSTUS2027</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -10914,19 +10914,19 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA21AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>OR22OKTOBER2027</t>
+          <t>SA22AGUSTUS2027</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -10939,19 +10939,19 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA22AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>OR23OKTOBER2027</t>
+          <t>SA23AGUSTUS2027</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -10964,19 +10964,19 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA23AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>OR24OKTOBER2027</t>
+          <t>SA24AGUSTUS2027</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -10989,19 +10989,19 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA24AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>OR25OKTOBER2027</t>
+          <t>SA25AGUSTUS2027</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -11014,19 +11014,19 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA25AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>OR26OKTOBER2027</t>
+          <t>SA26AGUSTUS2027</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -11039,19 +11039,19 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA26AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>OR27OKTOBER2027</t>
+          <t>SA27AGUSTUS2027</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -11064,19 +11064,19 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA27AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>OR28OKTOBER2027</t>
+          <t>SA28AGUSTUS2027</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -11089,19 +11089,19 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA28AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>OR29OKTOBER2027</t>
+          <t>SA29AGUSTUS2027</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -11114,19 +11114,19 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA29AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>OR30OKTOBER2027</t>
+          <t>SA30AGUSTUS2027</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -11139,19 +11139,19 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA30AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>OR31OKTOBER2027</t>
+          <t>SA31AGUSTUS2027</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -11164,14 +11164,14 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/SA31AGUSTUS2027</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>sutsugA</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/sutsugA/main/update_github_file.py</t>
         </is>
       </c>
     </row>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -446,16 +446,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>851</v>
+        <v>1834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>857297</v>
+        <v>13580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>857297</v>
+        <v>3878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>857297</v>
+        <v>851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -589,23 +589,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -614,23 +614,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -639,23 +639,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -689,23 +689,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -739,23 +739,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -764,23 +764,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -814,23 +814,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -839,23 +839,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -864,23 +864,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -889,23 +889,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -914,23 +914,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1014,23 +1014,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1039,23 +1039,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1064,23 +1064,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1089,23 +1089,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1114,23 +1114,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1139,23 +1139,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1189,23 +1189,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1214,23 +1214,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14656</v>
+        <v>857301</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1239,23 +1239,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>851</v>
+        <v>14664</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1264,23 +1264,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>857302</v>
+        <v>851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>857302</v>
+        <v>857298</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>14666</v>
+        <v>857298</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1834</v>
+        <v>857298</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>13580</v>
+        <v>14658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3878</v>
+        <v>851</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>851</v>
+        <v>857296</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IF01FEBRUARI2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IF02FEBRUARI2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IF03FEBRUARI2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IF04FEBRUARI2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IF05FEBRUARI2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IF06FEBRUARI2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IF07FEBRUARI2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IF08FEBRUARI2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IF09FEBRUARI2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IF10FEBRUARI2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IF11FEBRUARI2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IF12FEBRUARI2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IF13FEBRUARI2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IF14FEBRUARI2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IF15FEBRUARI2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IF16FEBRUARI2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IF17FEBRUARI2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IF18FEBRUARI2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IF19FEBRUARI2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IF20FEBRUARI2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IF21FEBRUARI2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IF22FEBRUARI2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IF23FEBRUARI2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IF24FEBRUARI2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IF25FEBRUARI2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IF26FEBRUARI2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IF27FEBRUARI2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IF28FEBRUARI2027</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>857301</v>
+        <v>857296</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>14664</v>
+        <v>857296</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>851</v>
+        <v>857296</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>857300</v>
+        <v>14654</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>857300</v>
+        <v>851</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,23 +2939,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,23 +2964,23 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3039,23 +3039,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3064,23 +3064,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3114,23 +3114,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3139,23 +3139,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3164,23 +3164,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3289,23 +3289,23 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3314,23 +3314,23 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3364,23 +3364,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3389,23 +3389,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3414,23 +3414,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3439,23 +3439,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3489,23 +3489,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3539,23 +3539,23 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3614,23 +3614,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3639,23 +3639,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>857300</v>
+        <v>857297</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3664,23 +3664,23 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>14662</v>
+        <v>857297</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>851</v>
+        <v>14656</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>857296</v>
+        <v>851</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>857296</v>
+        <v>857301</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>14654</v>
+        <v>857301</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>851</v>
+        <v>14664</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NR01NOVEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>584855</v>
+        <v>851</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,23 +4564,23 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NR02NOVEMBER2027</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,23 +4589,23 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NR03NOVEMBER2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4614,23 +4614,23 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NR04NOVEMBER2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4639,23 +4639,23 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>NR05NOVEMBER2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4664,23 +4664,23 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NR06NOVEMBER2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4689,23 +4689,23 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>NR07NOVEMBER2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NR08NOVEMBER2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4739,23 +4739,23 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NR09NOVEMBER2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4764,23 +4764,23 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NR10NOVEMBER2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4789,23 +4789,23 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NR11NOVEMBER2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -4814,23 +4814,23 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NR12NOVEMBER2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4839,23 +4839,23 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>NR13NOVEMBER2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4864,23 +4864,23 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NR14NOVEMBER2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -4889,23 +4889,23 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>NR15NOVEMBER2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4914,23 +4914,23 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NR16NOVEMBER2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4939,23 +4939,23 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NR17NOVEMBER2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>NR18NOVEMBER2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -4989,23 +4989,23 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NR19NOVEMBER2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5014,23 +5014,23 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NR20NOVEMBER2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5039,23 +5039,23 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NR21NOVEMBER2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5064,23 +5064,23 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NR22NOVEMBER2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NR23NOVEMBER2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -5114,23 +5114,23 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NR24NOVEMBER2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -5139,23 +5139,23 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NR25NOVEMBER2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -5164,23 +5164,23 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NR26NOVEMBER2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -5189,23 +5189,23 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NR27NOVEMBER2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -5214,23 +5214,23 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NR28NOVEMBER2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -5239,23 +5239,23 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NR29NOVEMBER2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -5264,23 +5264,23 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NR30NOVEMBER2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>584855</v>
+        <v>857302</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>14664</v>
+        <v>857302</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,23 +5314,23 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>851</v>
+        <v>14666</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -5351,11 +5351,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JL01JULI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>857297</v>
+        <v>851</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JL02JULI2027</t>
+          <t>JL01JULI2027</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JL03JULI2027</t>
+          <t>JL02JULI2027</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JL04JULI2027</t>
+          <t>JL03JULI2027</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JL05JULI2027</t>
+          <t>JL04JULI2027</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JL06JULI2027</t>
+          <t>JL05JULI2027</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JL07JULI2027</t>
+          <t>JL06JULI2027</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JL08JULI2027</t>
+          <t>JL07JULI2027</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JL09JULI2027</t>
+          <t>JL08JULI2027</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JL10JULI2027</t>
+          <t>JL09JULI2027</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JL11JULI2027</t>
+          <t>JL10JULI2027</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JL12JULI2027</t>
+          <t>JL11JULI2027</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JL13JULI2027</t>
+          <t>JL12JULI2027</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JL14JULI2027</t>
+          <t>JL13JULI2027</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JL15JULI2027</t>
+          <t>JL14JULI2027</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JL16JULI2027</t>
+          <t>JL15JULI2027</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JL17JULI2027</t>
+          <t>JL16JULI2027</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JL18JULI2027</t>
+          <t>JL17JULI2027</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>JL19JULI2027</t>
+          <t>JL18JULI2027</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JL20JULI2027</t>
+          <t>JL19JULI2027</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>JL21JULI2027</t>
+          <t>JL20JULI2027</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JL22JULI2027</t>
+          <t>JL21JULI2027</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JL23JULI2027</t>
+          <t>JL22JULI2027</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JL24JULI2027</t>
+          <t>JL23JULI2027</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JL25JULI2027</t>
+          <t>JL24JULI2027</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JL26JULI2027</t>
+          <t>JL25JULI2027</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JL27JULI2027</t>
+          <t>JL26JULI2027</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JL28JULI2027</t>
+          <t>JL27JULI2027</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JL29JULI2027</t>
+          <t>JL28JULI2027</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JL30JULI2027</t>
+          <t>JL29JULI2027</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JL31JULI2027</t>
+          <t>JL30JULI2027</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
         </is>
       </c>
     </row>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>JL31JULI2027</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>14656</v>
+        <v>857297</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,23 +6139,23 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>851</v>
+        <v>14656</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,23 +6164,23 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>857301</v>
+        <v>851</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6189,23 +6189,23 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>NR01NOVEMBER2027</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6214,23 +6214,23 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>NR02NOVEMBER2027</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6239,23 +6239,23 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>NR03NOVEMBER2027</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6264,23 +6264,23 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>NR04NOVEMBER2027</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6289,23 +6289,23 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>NR05NOVEMBER2027</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6314,23 +6314,23 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>NR06NOVEMBER2027</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6339,23 +6339,23 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>NR07NOVEMBER2027</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>NR08NOVEMBER2027</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6389,23 +6389,23 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>NR09NOVEMBER2027</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6414,23 +6414,23 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>NR10NOVEMBER2027</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>NR11NOVEMBER2027</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>NR12NOVEMBER2027</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>NR13NOVEMBER2027</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -6514,23 +6514,23 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>NR14NOVEMBER2027</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -6539,23 +6539,23 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>NR15NOVEMBER2027</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -6564,23 +6564,23 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>NR16NOVEMBER2027</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>NR17NOVEMBER2027</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -6614,23 +6614,23 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>NR18NOVEMBER2027</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>NR19NOVEMBER2027</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -6664,23 +6664,23 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>NR20NOVEMBER2027</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -6689,23 +6689,23 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>NR21NOVEMBER2027</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>NR22NOVEMBER2027</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>NR23NOVEMBER2027</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -6764,23 +6764,23 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>NR24NOVEMBER2027</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -6789,23 +6789,23 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>NR25NOVEMBER2027</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -6814,23 +6814,23 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>NR26NOVEMBER2027</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -6839,23 +6839,23 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>NR27NOVEMBER2027</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -6864,23 +6864,23 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>NR28NOVEMBER2027</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -6889,23 +6889,23 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>NR29NOVEMBER2027</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -6914,23 +6914,23 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>NR30NOVEMBER2027</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -6939,14 +6939,14 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6964,14 +6964,14 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6989,23 +6989,23 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,23 +7014,23 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>857298</v>
+        <v>857300</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>14658</v>
+        <v>14662</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16327</v>
+        <v>16248</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -446,16 +446,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1834</v>
+        <v>851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13580</v>
+        <v>857301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3878</v>
+        <v>857301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -526,11 +526,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>851</v>
+        <v>857301</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IF01FEBRUARI2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IF02FEBRUARI2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IF03FEBRUARI2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IF04FEBRUARI2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -639,7 +639,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IF05FEBRUARI2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IF06FEBRUARI2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IF07FEBRUARI2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IF08FEBRUARI2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IF09FEBRUARI2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IF10FEBRUARI2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IF11FEBRUARI2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IF12FEBRUARI2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IF13FEBRUARI2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IF14FEBRUARI2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IF15FEBRUARI2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IF16FEBRUARI2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IF17FEBRUARI2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IF18FEBRUARI2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IF19FEBRUARI2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IF20FEBRUARI2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IF21FEBRUARI2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IF22FEBRUARI2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IF23FEBRUARI2027</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IF24FEBRUARI2027</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IF25FEBRUARI2027</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
@@ -1176,11 +1176,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IF26FEBRUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>857301</v>
+        <v>14664</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1189,23 +1189,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IF27FEBRUARI2027</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>857301</v>
+        <v>1834</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1214,23 +1214,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IF28FEBRUARI2027</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>857301</v>
+        <v>13580</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1239,23 +1239,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14664</v>
+        <v>3878</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>857298</v>
+        <v>857297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>857298</v>
+        <v>14656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14658</v>
+        <v>851</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -2101,11 +2101,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>851</v>
+        <v>857296</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
@@ -2876,11 +2876,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>857296</v>
+        <v>14654</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>14654</v>
+        <v>851</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>JL01JULI2027</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>851</v>
+        <v>857297</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,19 +2939,19 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>JL02JULI2027</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2964,19 +2964,19 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>JL03JULI2027</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2989,19 +2989,19 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>JL04JULI2027</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>JL05JULI2027</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3039,19 +3039,19 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>JL06JULI2027</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3064,19 +3064,19 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>JL07JULI2027</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3089,19 +3089,19 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>JL08JULI2027</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3114,19 +3114,19 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>JL09JULI2027</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3139,19 +3139,19 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>JL10JULI2027</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3164,19 +3164,19 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>JL11JULI2027</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3189,19 +3189,19 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>JL12JULI2027</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>JL13JULI2027</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3239,19 +3239,19 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>JL14JULI2027</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3264,19 +3264,19 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>JL15JULI2027</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3289,19 +3289,19 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>JL16JULI2027</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3314,19 +3314,19 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>JL17JULI2027</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>JL18JULI2027</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3364,19 +3364,19 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>JL19JULI2027</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3389,19 +3389,19 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>JL20JULI2027</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3414,19 +3414,19 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>JL21JULI2027</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3439,19 +3439,19 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>JL22JULI2027</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3464,19 +3464,19 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>JL23JULI2027</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3489,19 +3489,19 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>JL24JULI2027</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3514,19 +3514,19 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>JL25JULI2027</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3539,19 +3539,19 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>JL26JULI2027</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3564,19 +3564,19 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>JL27JULI2027</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3589,19 +3589,19 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>JL28JULI2027</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3614,19 +3614,19 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>JL29JULI2027</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3639,19 +3639,19 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>JL30JULI2027</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>JL31JULI2027</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3689,14 +3689,14 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3714,14 +3714,14 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>NR01NOVEMBER2027</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>NR02NOVEMBER2027</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>NR03NOVEMBER2027</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>NR04NOVEMBER2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>NR05NOVEMBER2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>NR06NOVEMBER2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>NR07NOVEMBER2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>NR08NOVEMBER2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>NR09NOVEMBER2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>NR10NOVEMBER2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>NR11NOVEMBER2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>NR12NOVEMBER2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>NR13NOVEMBER2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>NR14NOVEMBER2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>NR15NOVEMBER2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>NR16NOVEMBER2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>NR17NOVEMBER2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>NR18NOVEMBER2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>NR19NOVEMBER2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>NR20NOVEMBER2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>NR21NOVEMBER2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>NR22NOVEMBER2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>NR23NOVEMBER2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>NR24NOVEMBER2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>NR25NOVEMBER2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>NR26NOVEMBER2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>NR27NOVEMBER2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>NR28NOVEMBER2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>NR29NOVEMBER2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>NR30NOVEMBER2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>857301</v>
+        <v>584855</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmevoN</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>857301</v>
+        <v>14664</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>14664</v>
+        <v>851</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -4551,11 +4551,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>851</v>
+        <v>857302</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
@@ -5301,11 +5301,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>857302</v>
+        <v>14666</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,23 +5314,23 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>14666</v>
+        <v>851</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5339,23 +5339,23 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>851</v>
+        <v>857301</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JL01JULI2027</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JL02JULI2027</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JL03JULI2027</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JL04JULI2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JL05JULI2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JL06JULI2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JL07JULI2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JL08JULI2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JL09JULI2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JL10JULI2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JL11JULI2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JL12JULI2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JL13JULI2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JL14JULI2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JL15JULI2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JL16JULI2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JL17JULI2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>JL18JULI2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JL19JULI2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>JL20JULI2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JL21JULI2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JL22JULI2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JL23JULI2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JL24JULI2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JL25JULI2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JL26JULI2027</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JL27JULI2027</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JL28JULI2027</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JL29JULI2027</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JL30JULI2027</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>857297</v>
+        <v>857301</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JL31JULI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>857297</v>
+        <v>14664</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,23 +6139,23 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>14656</v>
+        <v>851</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,23 +6164,23 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>851</v>
+        <v>857300</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6189,23 +6189,23 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>NR01NOVEMBER2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6214,23 +6214,23 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>NR02NOVEMBER2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6239,23 +6239,23 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>NR03NOVEMBER2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6264,23 +6264,23 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NR04NOVEMBER2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6289,23 +6289,23 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>NR05NOVEMBER2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6314,23 +6314,23 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>NR06NOVEMBER2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6339,23 +6339,23 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>NR07NOVEMBER2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>NR08NOVEMBER2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6389,23 +6389,23 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>NR09NOVEMBER2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6414,23 +6414,23 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>NR10NOVEMBER2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>NR11NOVEMBER2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>NR12NOVEMBER2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>NR13NOVEMBER2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -6514,23 +6514,23 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>NR14NOVEMBER2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -6539,23 +6539,23 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>NR15NOVEMBER2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -6564,23 +6564,23 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>NR16NOVEMBER2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>NR17NOVEMBER2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -6614,23 +6614,23 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>NR18NOVEMBER2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>NR19NOVEMBER2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -6664,23 +6664,23 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>NR20NOVEMBER2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -6689,23 +6689,23 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>NR21NOVEMBER2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>NR22NOVEMBER2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>NR23NOVEMBER2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -6764,23 +6764,23 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>NR24NOVEMBER2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -6789,23 +6789,23 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>NR25NOVEMBER2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -6814,23 +6814,23 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>NR26NOVEMBER2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -6839,23 +6839,23 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>NR27NOVEMBER2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -6864,23 +6864,23 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>NR28NOVEMBER2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -6889,23 +6889,23 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>NR29NOVEMBER2027</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -6914,23 +6914,23 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR29NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>NR30NOVEMBER2027</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>584855</v>
+        <v>857300</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -6939,14 +6939,14 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR30NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>14664</v>
+        <v>14662</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -6964,14 +6964,14 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6989,23 +6989,23 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,23 +7014,23 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>857300</v>
+        <v>857298</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>14662</v>
+        <v>14658</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16248</v>
+        <v>16448</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JL01JULI2027</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JL02JULI2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JL03JULI2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JL04JULI2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JL05JULI2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -589,23 +589,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JL06JULI2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -614,23 +614,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JL07JULI2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -639,23 +639,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JL08JULI2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JL09JULI2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -689,23 +689,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JL10JULI2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JL11JULI2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -739,23 +739,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JL12JULI2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -764,23 +764,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JL13JULI2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JL14JULI2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -814,23 +814,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JL15JULI2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -839,23 +839,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JL16JULI2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -864,23 +864,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JL17JULI2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -889,23 +889,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JL18JULI2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -914,23 +914,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JL19JULI2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JL20JULI2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JL21JULI2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JL22JULI2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1014,23 +1014,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JL23JULI2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1039,23 +1039,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JL24JULI2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1064,23 +1064,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JL25JULI2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1089,23 +1089,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JL26JULI2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1114,23 +1114,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JL27JULI2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1139,23 +1139,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JL28JULI2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JL29JULI2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1189,23 +1189,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JL30JULI2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1214,23 +1214,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JL31JULI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>874372</v>
+        <v>14666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14656</v>
+        <v>851</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1264,23 +1264,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>JL01JULI2027</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>851</v>
+        <v>874372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IF01FEBRUARI2027</t>
+          <t>JL02JULI2027</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IF02FEBRUARI2027</t>
+          <t>JL03JULI2027</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IF03FEBRUARI2027</t>
+          <t>JL04JULI2027</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IF04FEBRUARI2027</t>
+          <t>JL05JULI2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IF05FEBRUARI2027</t>
+          <t>JL06JULI2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IF06FEBRUARI2027</t>
+          <t>JL07JULI2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IF07FEBRUARI2027</t>
+          <t>JL08JULI2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IF08FEBRUARI2027</t>
+          <t>JL09JULI2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IF09FEBRUARI2027</t>
+          <t>JL10JULI2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IF10FEBRUARI2027</t>
+          <t>JL11JULI2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IF11FEBRUARI2027</t>
+          <t>JL12JULI2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IF12FEBRUARI2027</t>
+          <t>JL13JULI2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IF13FEBRUARI2027</t>
+          <t>JL14JULI2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IF14FEBRUARI2027</t>
+          <t>JL15JULI2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IF15FEBRUARI2027</t>
+          <t>JL16JULI2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IF16FEBRUARI2027</t>
+          <t>JL17JULI2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IF17FEBRUARI2027</t>
+          <t>JL18JULI2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IF18FEBRUARI2027</t>
+          <t>JL19JULI2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IF19FEBRUARI2027</t>
+          <t>JL20JULI2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IF20FEBRUARI2027</t>
+          <t>JL21JULI2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IF21FEBRUARI2027</t>
+          <t>JL22JULI2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IF22FEBRUARI2027</t>
+          <t>JL23JULI2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IF23FEBRUARI2027</t>
+          <t>JL24JULI2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IF24FEBRUARI2027</t>
+          <t>JL25JULI2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IF25FEBRUARI2027</t>
+          <t>JL26JULI2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IF26FEBRUARI2027</t>
+          <t>JL27JULI2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IF27FEBRUARI2027</t>
+          <t>JL28JULI2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IF28FEBRUARI2027</t>
+          <t>JL29JULI2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>874376</v>
+        <v>874372</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iraurbeF</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>JL30JULI2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>14664</v>
+        <v>874372</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>JL31JULI2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>851</v>
+        <v>874372</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>874371</v>
+        <v>14656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>874371</v>
+        <v>1834</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>874371</v>
+        <v>13580</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>874371</v>
+        <v>3878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>874371</v>
+        <v>851</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>874371</v>
+        <v>874376</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>14654</v>
+        <v>874376</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>851</v>
+        <v>874376</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,23 +2939,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>874372</v>
+        <v>14664</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,23 +2964,23 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>874372</v>
+        <v>851</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3039,23 +3039,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3064,23 +3064,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3114,23 +3114,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3139,23 +3139,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3164,23 +3164,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3289,23 +3289,23 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3314,23 +3314,23 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3364,23 +3364,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3389,23 +3389,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3414,23 +3414,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3439,23 +3439,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3489,23 +3489,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3539,23 +3539,23 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>874372</v>
+        <v>874376</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3614,23 +3614,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>14656</v>
+        <v>874376</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3639,23 +3639,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>851</v>
+        <v>874376</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3664,19 +3664,19 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>874376</v>
+        <v>14664</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>874376</v>
+        <v>851</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>14664</v>
+        <v>874371</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>851</v>
+        <v>874371</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>874377</v>
+        <v>874371</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>874377</v>
+        <v>14654</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>874377</v>
+        <v>851</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,23 +4564,23 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,23 +4589,23 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4614,23 +4614,23 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -4639,23 +4639,23 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4664,23 +4664,23 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -4689,23 +4689,23 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4739,23 +4739,23 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4764,23 +4764,23 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4789,23 +4789,23 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -4814,23 +4814,23 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4839,23 +4839,23 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4864,23 +4864,23 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -4889,23 +4889,23 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4914,23 +4914,23 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4939,23 +4939,23 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -4989,23 +4989,23 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5014,23 +5014,23 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5039,23 +5039,23 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -5064,23 +5064,23 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -5114,23 +5114,23 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -5139,23 +5139,23 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -5164,23 +5164,23 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -5189,23 +5189,23 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -5214,23 +5214,23 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -5239,23 +5239,23 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>14666</v>
+        <v>874372</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -5264,23 +5264,23 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>851</v>
+        <v>874372</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,23 +5314,23 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>874375</v>
+        <v>14656</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -5339,23 +5339,23 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>874375</v>
+        <v>851</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>14662</v>
+        <v>874373</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>1834</v>
+        <v>874373</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>13580</v>
+        <v>874373</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,23 +6139,23 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3878</v>
+        <v>14658</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6989,23 +6989,23 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,23 +7014,23 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>14658</v>
+        <v>14662</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,14 +7789,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7814,23 +7814,23 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>OR01OKTOBER2027</t>
+          <t>MT01MARET2027</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -7839,23 +7839,23 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>OR02OKTOBER2027</t>
+          <t>MT02MARET2027</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -7864,23 +7864,23 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>OR03OKTOBER2027</t>
+          <t>MT03MARET2027</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -7889,23 +7889,23 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>OR04OKTOBER2027</t>
+          <t>MT04MARET2027</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -7914,23 +7914,23 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>OR05OKTOBER2027</t>
+          <t>MT05MARET2027</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -7939,23 +7939,23 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>OR06OKTOBER2027</t>
+          <t>MT06MARET2027</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -7964,23 +7964,23 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>OR07OKTOBER2027</t>
+          <t>MT07MARET2027</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -7989,23 +7989,23 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>OR08OKTOBER2027</t>
+          <t>MT08MARET2027</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -8014,23 +8014,23 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>OR09OKTOBER2027</t>
+          <t>MT09MARET2027</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -8039,23 +8039,23 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>OR10OKTOBER2027</t>
+          <t>MT10MARET2027</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -8064,23 +8064,23 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>OR11OKTOBER2027</t>
+          <t>MT11MARET2027</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -8089,23 +8089,23 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>OR12OKTOBER2027</t>
+          <t>MT12MARET2027</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -8114,23 +8114,23 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>OR13OKTOBER2027</t>
+          <t>MT13MARET2027</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -8139,23 +8139,23 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>OR14OKTOBER2027</t>
+          <t>MT14MARET2027</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -8164,23 +8164,23 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>OR15OKTOBER2027</t>
+          <t>MT15MARET2027</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -8189,23 +8189,23 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>OR16OKTOBER2027</t>
+          <t>MT16MARET2027</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -8214,23 +8214,23 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>OR17OKTOBER2027</t>
+          <t>MT17MARET2027</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -8239,23 +8239,23 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>OR18OKTOBER2027</t>
+          <t>MT18MARET2027</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -8264,23 +8264,23 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>OR19OKTOBER2027</t>
+          <t>MT19MARET2027</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -8289,23 +8289,23 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>OR20OKTOBER2027</t>
+          <t>MT20MARET2027</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>OR21OKTOBER2027</t>
+          <t>MT21MARET2027</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -8339,23 +8339,23 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>OR22OKTOBER2027</t>
+          <t>MT22MARET2027</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -8364,23 +8364,23 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>OR23OKTOBER2027</t>
+          <t>MT23MARET2027</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -8389,23 +8389,23 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>OR24OKTOBER2027</t>
+          <t>MT24MARET2027</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -8414,23 +8414,23 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>OR25OKTOBER2027</t>
+          <t>MT25MARET2027</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -8439,23 +8439,23 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>OR26OKTOBER2027</t>
+          <t>MT26MARET2027</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -8464,23 +8464,23 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>OR27OKTOBER2027</t>
+          <t>MT27MARET2027</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -8489,23 +8489,23 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>OR28OKTOBER2027</t>
+          <t>MT28MARET2027</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -8514,23 +8514,23 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>OR29OKTOBER2027</t>
+          <t>MT29MARET2027</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -8539,23 +8539,23 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>OR30OKTOBER2027</t>
+          <t>MT30MARET2027</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -8564,23 +8564,23 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>OR31OKTOBER2027</t>
+          <t>MT31MARET2027</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>14662</v>
+        <v>14656</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16374</v>
+        <v>16401</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8789,23 +8789,23 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MT01MARET2027</t>
+          <t>OR01OKTOBER2027</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -8814,23 +8814,23 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MT02MARET2027</t>
+          <t>OR02OKTOBER2027</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -8839,23 +8839,23 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>MT03MARET2027</t>
+          <t>OR03OKTOBER2027</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -8864,23 +8864,23 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MT04MARET2027</t>
+          <t>OR04OKTOBER2027</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -8889,23 +8889,23 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MT05MARET2027</t>
+          <t>OR05OKTOBER2027</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -8914,23 +8914,23 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>MT06MARET2027</t>
+          <t>OR06OKTOBER2027</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -8939,23 +8939,23 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>MT07MARET2027</t>
+          <t>OR07OKTOBER2027</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -8964,23 +8964,23 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>MT08MARET2027</t>
+          <t>OR08OKTOBER2027</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -8989,23 +8989,23 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>MT09MARET2027</t>
+          <t>OR09OKTOBER2027</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -9014,23 +9014,23 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>MT10MARET2027</t>
+          <t>OR10OKTOBER2027</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -9039,23 +9039,23 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>MT11MARET2027</t>
+          <t>OR11OKTOBER2027</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -9064,23 +9064,23 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>MT12MARET2027</t>
+          <t>OR12OKTOBER2027</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -9089,23 +9089,23 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>MT13MARET2027</t>
+          <t>OR13OKTOBER2027</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -9114,23 +9114,23 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MT14MARET2027</t>
+          <t>OR14OKTOBER2027</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -9139,23 +9139,23 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MT15MARET2027</t>
+          <t>OR15OKTOBER2027</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -9164,23 +9164,23 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MT16MARET2027</t>
+          <t>OR16OKTOBER2027</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -9189,23 +9189,23 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MT17MARET2027</t>
+          <t>OR17OKTOBER2027</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -9214,23 +9214,23 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MT18MARET2027</t>
+          <t>OR18OKTOBER2027</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -9239,23 +9239,23 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>MT19MARET2027</t>
+          <t>OR19OKTOBER2027</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -9264,23 +9264,23 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>MT20MARET2027</t>
+          <t>OR20OKTOBER2027</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -9289,23 +9289,23 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>MT21MARET2027</t>
+          <t>OR21OKTOBER2027</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -9314,23 +9314,23 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MT22MARET2027</t>
+          <t>OR22OKTOBER2027</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -9339,23 +9339,23 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>MT23MARET2027</t>
+          <t>OR23OKTOBER2027</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -9364,23 +9364,23 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MT24MARET2027</t>
+          <t>OR24OKTOBER2027</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -9389,23 +9389,23 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>MT25MARET2027</t>
+          <t>OR25OKTOBER2027</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -9414,23 +9414,23 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MT26MARET2027</t>
+          <t>OR26OKTOBER2027</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -9439,23 +9439,23 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MT27MARET2027</t>
+          <t>OR27OKTOBER2027</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -9464,23 +9464,23 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MT28MARET2027</t>
+          <t>OR28OKTOBER2027</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -9489,23 +9489,23 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MT29MARET2027</t>
+          <t>OR29OKTOBER2027</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -9514,23 +9514,23 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MT30MARET2027</t>
+          <t>OR30OKTOBER2027</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -9539,23 +9539,23 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MT31MARET2027</t>
+          <t>OR31OKTOBER2027</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -9564,14 +9564,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>14656</v>
+        <v>14662</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
         </is>
       </c>
     </row>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -446,16 +446,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>.github/workflows/shorten-urls.yml</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1834</v>
+        <v>851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -464,23 +464,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>JL01JULI2027</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13580</v>
+        <v>874372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alturl_bulk_shorten.py</t>
+          <t>iluJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hasil_shorturl.csv</t>
+          <t>JL02JULI2027</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3878</v>
+        <v>874372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
         </is>
       </c>
     </row>
@@ -526,11 +526,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>JL03JULI2027</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>851</v>
+        <v>874372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JL01JULI2027</t>
+          <t>JL04JULI2027</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL01JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JL02JULI2027</t>
+          <t>JL05JULI2027</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL02JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JL03JULI2027</t>
+          <t>JL06JULI2027</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL03JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JL04JULI2027</t>
+          <t>JL07JULI2027</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -639,7 +639,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL04JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JL05JULI2027</t>
+          <t>JL08JULI2027</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL05JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JL06JULI2027</t>
+          <t>JL09JULI2027</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL06JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JL07JULI2027</t>
+          <t>JL10JULI2027</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL07JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JL08JULI2027</t>
+          <t>JL11JULI2027</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL08JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JL09JULI2027</t>
+          <t>JL12JULI2027</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL09JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JL10JULI2027</t>
+          <t>JL13JULI2027</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL10JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JL11JULI2027</t>
+          <t>JL14JULI2027</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL11JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JL12JULI2027</t>
+          <t>JL15JULI2027</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL12JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JL13JULI2027</t>
+          <t>JL16JULI2027</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL13JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JL14JULI2027</t>
+          <t>JL17JULI2027</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL14JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JL15JULI2027</t>
+          <t>JL18JULI2027</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL15JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JL16JULI2027</t>
+          <t>JL19JULI2027</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL16JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JL17JULI2027</t>
+          <t>JL20JULI2027</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL17JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JL18JULI2027</t>
+          <t>JL21JULI2027</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL18JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JL19JULI2027</t>
+          <t>JL22JULI2027</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL19JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JL20JULI2027</t>
+          <t>JL23JULI2027</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL20JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JL21JULI2027</t>
+          <t>JL24JULI2027</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL21JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JL22JULI2027</t>
+          <t>JL25JULI2027</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL22JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JL23JULI2027</t>
+          <t>JL26JULI2027</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL23JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JL24JULI2027</t>
+          <t>JL27JULI2027</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL24JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JL25JULI2027</t>
+          <t>JL28JULI2027</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL25JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JL26JULI2027</t>
+          <t>JL29JULI2027</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL26JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JL27JULI2027</t>
+          <t>JL30JULI2027</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL27JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JL28JULI2027</t>
+          <t>JL31JULI2027</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL28JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
         </is>
       </c>
     </row>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JL29JULI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>874372</v>
+        <v>14656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1264,23 +1264,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL29JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JL30JULI2027</t>
+          <t>.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>874372</v>
+        <v>1834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1289,23 +1289,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL30JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/.github/workflows/shorten-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JL31JULI2027</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>874372</v>
+        <v>13580</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/JL31JULI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/alturl_bulk_shorten.py</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iluJ</t>
+          <t>alturl_bulk_shorten.py</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>hasil_shorturl.csv</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14656</v>
+        <v>3878</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,14 +1339,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/iluJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/alturl_bulk_shorten.py/main/hasil_shorturl.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>AL01MARET2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>AL02MARET2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>AL03MARET2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>AL04MARET2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>AL05MARET2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>AL06MARET2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>AL07MARET2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>AL08MARET2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>AL09MARET2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>AL10MARET2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>AL11MARET2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>AL12MARET2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>AL13MARET2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>AL14MARET2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>AL15MARET2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>AL16MARET2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>AL17MARET2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>AL18MARET2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>AL19MARET2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>AL20MARET2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>AL21MARET2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>AL22MARET2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>AL23MARET2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>AL24MARET2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>AL25MARET2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>AL26MARET2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>AL27MARET2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>AL28MARET2027</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>AL29MARET2027</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>AL30MARET2027</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>874372</v>
+        <v>874373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>lirpA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>AL31MARET2027</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>14656</v>
+        <v>874373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
         </is>
       </c>
     </row>
@@ -2151,11 +2151,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>851</v>
+        <v>14658</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AL01MARET2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>874373</v>
+        <v>851</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AL02MARET2027</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AL03MARET2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AL04MARET2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AL05MARET2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AL06MARET2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AL07MARET2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AL08MARET2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AL09MARET2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AL10MARET2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AL11MARET2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AL12MARET2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AL13MARET2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AL14MARET2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AL15MARET2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AL16MARET2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AL17MARET2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AL18MARET2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AL19MARET2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AL20MARET2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AL21MARET2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AL22MARET2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AL23MARET2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AL24MARET2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AL25MARET2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AL26MARET2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AL27MARET2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AL28MARET2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AL29MARET2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AL30MARET2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AL31MARET2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>874373</v>
+        <v>874377</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/AL31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>lirpA</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>14658</v>
+        <v>14666</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,14 +2964,14 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/lirpA/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3039,23 +3039,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3064,23 +3064,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3114,23 +3114,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3139,23 +3139,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3164,23 +3164,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3289,23 +3289,23 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3314,23 +3314,23 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3364,23 +3364,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3389,23 +3389,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3414,23 +3414,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3439,23 +3439,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3489,23 +3489,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3539,23 +3539,23 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3614,23 +3614,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3639,23 +3639,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3664,23 +3664,23 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>874377</v>
+        <v>874372</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,14 +3739,14 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>14666</v>
+        <v>14656</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,14 +3764,14 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>DR01DESEMBER2027</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>DR02DESEMBER2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>DR03DESEMBER2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>DR04DESEMBER2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>DR05DESEMBER2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>DR06DESEMBER2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>DR07DESEMBER2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>DR08DESEMBER2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>DR09DESEMBER2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>DR10DESEMBER2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>DR11DESEMBER2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>DR12DESEMBER2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>DR13DESEMBER2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>DR14DESEMBER2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>DR15DESEMBER2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>DR16DESEMBER2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>DR17DESEMBER2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>DR18DESEMBER2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>DR19DESEMBER2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>DR20DESEMBER2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>DR21DESEMBER2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>DR22DESEMBER2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>DR23DESEMBER2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>DR24DESEMBER2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>DR25DESEMBER2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>DR26DESEMBER2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>DR27DESEMBER2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>DR28DESEMBER2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>DR29DESEMBER2027</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>DR30DESEMBER2027</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>DR31DESEMBER2027</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>874375</v>
+        <v>874376</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,14 +4564,14 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>rebmeseD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>14662</v>
+        <v>14664</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IM01MEI2027</t>
+          <t>MP01JANUARI2027</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IM02MEI2027</t>
+          <t>MP02JANUARI2027</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IM03MEI2027</t>
+          <t>MP03JANUARI2027</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IM04MEI2027</t>
+          <t>MP04JANUARI2027</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>IM05MEI2027</t>
+          <t>MP05JANUARI2027</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IM06MEI2027</t>
+          <t>MP06JANUARI2027</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>IM07MEI2027</t>
+          <t>MP07JANUARI2027</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IM08MEI2027</t>
+          <t>MP08JANUARI2027</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IM09MEI2027</t>
+          <t>MP09JANUARI2027</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IM10MEI2027</t>
+          <t>MP10JANUARI2027</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>IM11MEI2027</t>
+          <t>MP11JANUARI2027</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IM12MEI2027</t>
+          <t>MP12JANUARI2027</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IM13MEI2027</t>
+          <t>MP13JANUARI2027</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IM14MEI2027</t>
+          <t>MP14JANUARI2027</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>IM15MEI2027</t>
+          <t>MP15JANUARI2027</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IM16MEI2027</t>
+          <t>MP16JANUARI2027</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>IM17MEI2027</t>
+          <t>MP17JANUARI2027</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>IM18MEI2027</t>
+          <t>MP18JANUARI2027</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>IM19MEI2027</t>
+          <t>MP19JANUARI2027</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>IM20MEI2027</t>
+          <t>MP20JANUARI2027</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IM21MEI2027</t>
+          <t>MP21JANUARI2027</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IM22MEI2027</t>
+          <t>MP22JANUARI2027</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>IM23MEI2027</t>
+          <t>MP23JANUARI2027</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>IM24MEI2027</t>
+          <t>MP24JANUARI2027</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>IM25MEI2027</t>
+          <t>MP25JANUARI2027</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>IM26MEI2027</t>
+          <t>MP26JANUARI2027</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IM27MEI2027</t>
+          <t>MP27JANUARI2027</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IM28MEI2027</t>
+          <t>MP28JANUARI2027</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IM29MEI2027</t>
+          <t>MP29JANUARI2027</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>IM30MEI2027</t>
+          <t>MP30JANUARI2027</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IM31MEI2027</t>
+          <t>MP31JANUARI2027</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>874371</v>
+        <v>874375</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,14 +6139,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ieM</t>
+          <t>markpom</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>14654</v>
+        <v>14662</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6989,23 +6989,23 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DR01DESEMBER2027</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -7014,23 +7014,23 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR01DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DR02DESEMBER2027</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -7039,23 +7039,23 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR02DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DR03DESEMBER2027</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -7064,23 +7064,23 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR03DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DR04DESEMBER2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -7089,23 +7089,23 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR04DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DR05DESEMBER2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -7114,23 +7114,23 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR05DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DR06DESEMBER2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -7139,23 +7139,23 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR06DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DR07DESEMBER2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR07DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DR08DESEMBER2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -7189,23 +7189,23 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR08DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DR09DESEMBER2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -7214,23 +7214,23 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR09DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DR10DESEMBER2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -7239,23 +7239,23 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR10DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DR11DESEMBER2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -7264,23 +7264,23 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR11DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DR12DESEMBER2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -7289,23 +7289,23 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR12DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DR13DESEMBER2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -7314,23 +7314,23 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR13DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DR14DESEMBER2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -7339,23 +7339,23 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR14DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DR15DESEMBER2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR15DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DR16DESEMBER2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -7389,23 +7389,23 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR16DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DR17DESEMBER2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -7414,23 +7414,23 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR17DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DR18DESEMBER2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -7439,23 +7439,23 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR18DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DR19DESEMBER2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR19DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DR20DESEMBER2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -7489,23 +7489,23 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR20DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DR21DESEMBER2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -7514,23 +7514,23 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR21DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DR22DESEMBER2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -7539,23 +7539,23 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR22DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DR23DESEMBER2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -7564,23 +7564,23 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR23DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DR24DESEMBER2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -7589,23 +7589,23 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR24DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DR25DESEMBER2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7614,23 +7614,23 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR25DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DR26DESEMBER2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -7639,23 +7639,23 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR26DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DR27DESEMBER2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -7664,23 +7664,23 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR27DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DR28DESEMBER2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -7689,23 +7689,23 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR28DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>DR29DESEMBER2027</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR29DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DR30DESEMBER2027</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR30DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DR31DESEMBER2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>874376</v>
+        <v>874371</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/DR31DESEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>rebmeseD</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>14664</v>
+        <v>14654</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,14 +7789,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmeseD/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7814,23 +7814,23 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>OR01OKTOBER2027</t>
+          <t>MT01MARET2027</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -7839,23 +7839,23 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>OR02OKTOBER2027</t>
+          <t>MT02MARET2027</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -7864,23 +7864,23 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>OR03OKTOBER2027</t>
+          <t>MT03MARET2027</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -7889,23 +7889,23 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>OR04OKTOBER2027</t>
+          <t>MT04MARET2027</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -7914,23 +7914,23 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>OR05OKTOBER2027</t>
+          <t>MT05MARET2027</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -7939,23 +7939,23 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>OR06OKTOBER2027</t>
+          <t>MT06MARET2027</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -7964,23 +7964,23 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>OR07OKTOBER2027</t>
+          <t>MT07MARET2027</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -7989,23 +7989,23 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>OR08OKTOBER2027</t>
+          <t>MT08MARET2027</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -8014,23 +8014,23 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>OR09OKTOBER2027</t>
+          <t>MT09MARET2027</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -8039,23 +8039,23 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>OR10OKTOBER2027</t>
+          <t>MT10MARET2027</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -8064,23 +8064,23 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>OR11OKTOBER2027</t>
+          <t>MT11MARET2027</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -8089,23 +8089,23 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>OR12OKTOBER2027</t>
+          <t>MT12MARET2027</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -8114,23 +8114,23 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>OR13OKTOBER2027</t>
+          <t>MT13MARET2027</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -8139,23 +8139,23 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>OR14OKTOBER2027</t>
+          <t>MT14MARET2027</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -8164,23 +8164,23 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>OR15OKTOBER2027</t>
+          <t>MT15MARET2027</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -8189,23 +8189,23 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>OR16OKTOBER2027</t>
+          <t>MT16MARET2027</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -8214,23 +8214,23 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>OR17OKTOBER2027</t>
+          <t>MT17MARET2027</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -8239,23 +8239,23 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>OR18OKTOBER2027</t>
+          <t>MT18MARET2027</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -8264,23 +8264,23 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>OR19OKTOBER2027</t>
+          <t>MT19MARET2027</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -8289,23 +8289,23 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>OR20OKTOBER2027</t>
+          <t>MT20MARET2027</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>OR21OKTOBER2027</t>
+          <t>MT21MARET2027</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -8339,23 +8339,23 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>OR22OKTOBER2027</t>
+          <t>MT22MARET2027</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -8364,23 +8364,23 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>OR23OKTOBER2027</t>
+          <t>MT23MARET2027</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -8389,23 +8389,23 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>OR24OKTOBER2027</t>
+          <t>MT24MARET2027</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -8414,23 +8414,23 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>OR25OKTOBER2027</t>
+          <t>MT25MARET2027</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -8439,23 +8439,23 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>OR26OKTOBER2027</t>
+          <t>MT26MARET2027</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -8464,23 +8464,23 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>OR27OKTOBER2027</t>
+          <t>MT27MARET2027</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -8489,23 +8489,23 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>OR28OKTOBER2027</t>
+          <t>MT28MARET2027</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -8514,23 +8514,23 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>OR29OKTOBER2027</t>
+          <t>MT29MARET2027</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -8539,23 +8539,23 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>OR30OKTOBER2027</t>
+          <t>MT30MARET2027</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -8564,23 +8564,23 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>OR31OKTOBER2027</t>
+          <t>MT31MARET2027</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>874375</v>
+        <v>874373</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>rebotkO</t>
+          <t>teraM</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>14662</v>
+        <v>14656</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -8614,23 +8614,23 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>.github/workflows/raw-urls.yml</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2168</v>
+        <v>851</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -8639,23 +8639,23 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/.github/workflows/raw-urls.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>data/phxnkhlay_all_raw.csv</t>
+          <t>OR01OKTOBER2027</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>46466</v>
+        <v>874375</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -8664,23 +8664,23 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR01OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>data/phxnkhlay_all_raw.xlsx</t>
+          <t>OR02OKTOBER2027</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>16434</v>
+        <v>874375</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -8689,23 +8689,23 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.xlsx</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR02OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>data/uppermoon77_all_raw.csv</t>
+          <t>OR03OKTOBER2027</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>42049</v>
+        <v>874375</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -8714,23 +8714,23 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.csv</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR03OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>data/uppermoon77_all_raw.xlsx</t>
+          <t>OR04OKTOBER2027</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>15157</v>
+        <v>874375</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -8739,23 +8739,23 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.xlsx</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR04OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>URL-GENERATOR</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>generate_all_repos_raw_urls.py</t>
+          <t>OR05OKTOBER2027</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>6525</v>
+        <v>874375</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -8764,23 +8764,23 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/generate_all_repos_raw_urls.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR05OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>OR06OKTOBER2027</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>851</v>
+        <v>874375</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -8789,23 +8789,23 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR06OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MT01MARET2027</t>
+          <t>OR07OKTOBER2027</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -8814,23 +8814,23 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT01MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR07OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MT02MARET2027</t>
+          <t>OR08OKTOBER2027</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -8839,23 +8839,23 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT02MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR08OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>MT03MARET2027</t>
+          <t>OR09OKTOBER2027</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -8864,23 +8864,23 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT03MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR09OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MT04MARET2027</t>
+          <t>OR10OKTOBER2027</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -8889,23 +8889,23 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT04MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR10OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MT05MARET2027</t>
+          <t>OR11OKTOBER2027</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -8914,23 +8914,23 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT05MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR11OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>MT06MARET2027</t>
+          <t>OR12OKTOBER2027</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -8939,23 +8939,23 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT06MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR12OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>MT07MARET2027</t>
+          <t>OR13OKTOBER2027</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -8964,23 +8964,23 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT07MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR13OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>MT08MARET2027</t>
+          <t>OR14OKTOBER2027</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -8989,23 +8989,23 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT08MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR14OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>MT09MARET2027</t>
+          <t>OR15OKTOBER2027</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -9014,23 +9014,23 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT09MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR15OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>MT10MARET2027</t>
+          <t>OR16OKTOBER2027</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -9039,23 +9039,23 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT10MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR16OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>MT11MARET2027</t>
+          <t>OR17OKTOBER2027</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -9064,23 +9064,23 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT11MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR17OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>MT12MARET2027</t>
+          <t>OR18OKTOBER2027</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -9089,23 +9089,23 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT12MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR18OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>MT13MARET2027</t>
+          <t>OR19OKTOBER2027</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -9114,23 +9114,23 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT13MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR19OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MT14MARET2027</t>
+          <t>OR20OKTOBER2027</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -9139,23 +9139,23 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT14MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR20OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MT15MARET2027</t>
+          <t>OR21OKTOBER2027</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -9164,23 +9164,23 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT15MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR21OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MT16MARET2027</t>
+          <t>OR22OKTOBER2027</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -9189,23 +9189,23 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT16MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR22OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MT17MARET2027</t>
+          <t>OR23OKTOBER2027</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -9214,23 +9214,23 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT17MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR23OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MT18MARET2027</t>
+          <t>OR24OKTOBER2027</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -9239,23 +9239,23 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT18MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR24OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>MT19MARET2027</t>
+          <t>OR25OKTOBER2027</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -9264,23 +9264,23 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT19MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR25OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>MT20MARET2027</t>
+          <t>OR26OKTOBER2027</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -9289,23 +9289,23 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT20MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR26OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>MT21MARET2027</t>
+          <t>OR27OKTOBER2027</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -9314,23 +9314,23 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT21MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR27OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MT22MARET2027</t>
+          <t>OR28OKTOBER2027</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -9339,23 +9339,23 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT22MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR28OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>MT23MARET2027</t>
+          <t>OR29OKTOBER2027</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -9364,23 +9364,23 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT23MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR29OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MT24MARET2027</t>
+          <t>OR30OKTOBER2027</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -9389,23 +9389,23 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT24MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR30OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>MT25MARET2027</t>
+          <t>OR31OKTOBER2027</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>874373</v>
+        <v>874375</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -9414,23 +9414,23 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT25MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/OR31OKTOBER2027</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>rebotkO</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MT26MARET2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>874373</v>
+        <v>14662</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -9439,23 +9439,23 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT26MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebotkO/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MT27MARET2027</t>
+          <t>.github/workflows/raw-urls.yml</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>874373</v>
+        <v>2168</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -9464,23 +9464,23 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT27MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/.github/workflows/raw-urls.yml</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MT28MARET2027</t>
+          <t>data/phxnkhlay_all_raw.csv</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>874373</v>
+        <v>46466</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -9489,23 +9489,23 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT28MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.csv</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MT29MARET2027</t>
+          <t>data/phxnkhlay_all_raw.xlsx</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>874373</v>
+        <v>16273</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -9514,23 +9514,23 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT29MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/phxnkhlay_all_raw.xlsx</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MT30MARET2027</t>
+          <t>data/uppermoon77_all_raw.csv</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>874373</v>
+        <v>42049</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -9539,23 +9539,23 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT30MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.csv</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MT31MARET2027</t>
+          <t>data/uppermoon77_all_raw.xlsx</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>874373</v>
+        <v>15157</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -9564,23 +9564,23 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/MT31MARET2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/data/uppermoon77_all_raw.xlsx</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>teraM</t>
+          <t>URL-GENERATOR</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>generate_all_repos_raw_urls.py</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>14656</v>
+        <v>6525</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/teraM/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/URL-GENERATOR/main/generate_all_repos_raw_urls.py</t>
         </is>
       </c>
     </row>

--- a/data/phxnkhlay_all_raw.xlsx
+++ b/data/phxnkhlay_all_raw.xlsx
@@ -1346,7 +1346,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IJ01JUNI2027</t>
+          <t>SR01SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IJ02JUNI2027</t>
+          <t>SR02SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IJ03JUNI2027</t>
+          <t>SR03SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IJ04JUNI2027</t>
+          <t>SR04SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IJ05JUNI2027</t>
+          <t>SR05SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IJ06JUNI2027</t>
+          <t>SR06SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IJ07JUNI2027</t>
+          <t>SR07SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IJ08JUNI2027</t>
+          <t>SR08SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IJ09JUNI2027</t>
+          <t>SR09SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IJ10JUNI2027</t>
+          <t>SR10SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IJ11JUNI2027</t>
+          <t>SR11SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IJ12JUNI2027</t>
+          <t>SR12SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IJ13JUNI2027</t>
+          <t>SR13SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IJ14JUNI2027</t>
+          <t>SR14SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IJ15JUNI2027</t>
+          <t>SR15SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IJ16JUNI2027</t>
+          <t>SR16SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IJ17JUNI2027</t>
+          <t>SR17SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IJ18JUNI2027</t>
+          <t>SR18SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IJ19JUNI2027</t>
+          <t>SR19SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IJ20JUNI2027</t>
+          <t>SR20SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IJ21JUNI2027</t>
+          <t>SR21SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IJ22JUNI2027</t>
+          <t>SR22SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IJ23JUNI2027</t>
+          <t>SR23SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IJ24JUNI2027</t>
+          <t>SR24SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IJ25JUNI2027</t>
+          <t>SR25SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IJ26JUNI2027</t>
+          <t>SR26SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IJ27JUNI2027</t>
+          <t>SR27SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IJ28JUNI2027</t>
+          <t>SR28SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IJ29JUNI2027</t>
+          <t>SR29SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IJ30JUNI2027</t>
+          <t>SR30SEPTEMBER2027</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>874372</v>
+        <v>874377</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,14 +2114,14 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inuJ</t>
+          <t>rebmetpeS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>14656</v>
+        <v>14666</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,14 +2139,14 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SR01SEPTEMBER2027</t>
+          <t>IF01FEBRUARI2027</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR01SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF01FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SR02SEPTEMBER2027</t>
+          <t>IF02FEBRUARI2027</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR02SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF02FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SR03SEPTEMBER2027</t>
+          <t>IF03FEBRUARI2027</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR03SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF03FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SR04SEPTEMBER2027</t>
+          <t>IF04FEBRUARI2027</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR04SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF04FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SR05SEPTEMBER2027</t>
+          <t>IF05FEBRUARI2027</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR05SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF05FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SR06SEPTEMBER2027</t>
+          <t>IF06FEBRUARI2027</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR06SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF06FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SR07SEPTEMBER2027</t>
+          <t>IF07FEBRUARI2027</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR07SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF07FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SR08SEPTEMBER2027</t>
+          <t>IF08FEBRUARI2027</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR08SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF08FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SR09SEPTEMBER2027</t>
+          <t>IF09FEBRUARI2027</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR09SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF09FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SR10SEPTEMBER2027</t>
+          <t>IF10FEBRUARI2027</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR10SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF10FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SR11SEPTEMBER2027</t>
+          <t>IF11FEBRUARI2027</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR11SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF11FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SR12SEPTEMBER2027</t>
+          <t>IF12FEBRUARI2027</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR12SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF12FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SR13SEPTEMBER2027</t>
+          <t>IF13FEBRUARI2027</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR13SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF13FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SR14SEPTEMBER2027</t>
+          <t>IF14FEBRUARI2027</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR14SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF14FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SR15SEPTEMBER2027</t>
+          <t>IF15FEBRUARI2027</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR15SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF15FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SR16SEPTEMBER2027</t>
+          <t>IF16FEBRUARI2027</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR16SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF16FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SR17SEPTEMBER2027</t>
+          <t>IF17FEBRUARI2027</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR17SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF17FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SR18SEPTEMBER2027</t>
+          <t>IF18FEBRUARI2027</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR18SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF18FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SR19SEPTEMBER2027</t>
+          <t>IF19FEBRUARI2027</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR19SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF19FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SR20SEPTEMBER2027</t>
+          <t>IF20FEBRUARI2027</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR20SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF20FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SR21SEPTEMBER2027</t>
+          <t>IF21FEBRUARI2027</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR21SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF21FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SR22SEPTEMBER2027</t>
+          <t>IF22FEBRUARI2027</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR22SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF22FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SR23SEPTEMBER2027</t>
+          <t>IF23FEBRUARI2027</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR23SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF23FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SR24SEPTEMBER2027</t>
+          <t>IF24FEBRUARI2027</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR24SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF24FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SR25SEPTEMBER2027</t>
+          <t>IF25FEBRUARI2027</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR25SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF25FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SR26SEPTEMBER2027</t>
+          <t>IF26FEBRUARI2027</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR26SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF26FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SR27SEPTEMBER2027</t>
+          <t>IF27FEBRUARI2027</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR27SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF27FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SR28SEPTEMBER2027</t>
+          <t>IF28FEBRUARI2027</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>874377</v>
+        <v>874376</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR28SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/IF28FEBRUARI2027</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>iraurbeF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SR29SEPTEMBER2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>874377</v>
+        <v>14664</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR29SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/iraurbeF/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SR30SEPTEMBER2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>874377</v>
+        <v>851</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,23 +2914,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/SR30SEPTEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rebmetpeS</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IJ01JUNI2027</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>14666</v>
+        <v>874372</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,23 +2939,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmetpeS/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ01JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IJ02JUNI2027</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>851</v>
+        <v>874372</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2964,23 +2964,23 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ02JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MP01JANUARI2027</t>
+          <t>IJ03JUNI2027</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP01JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ03JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MP02JANUARI2027</t>
+          <t>IJ04JUNI2027</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3014,23 +3014,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP02JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ04JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MP03JANUARI2027</t>
+          <t>IJ05JUNI2027</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3039,23 +3039,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP03JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ05JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MP04JANUARI2027</t>
+          <t>IJ06JUNI2027</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3064,23 +3064,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP04JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ06JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MP05JANUARI2027</t>
+          <t>IJ07JUNI2027</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3089,23 +3089,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP05JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ07JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MP06JANUARI2027</t>
+          <t>IJ08JUNI2027</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3114,23 +3114,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP06JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ08JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MP07JANUARI2027</t>
+          <t>IJ09JUNI2027</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3139,23 +3139,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP07JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ09JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MP08JANUARI2027</t>
+          <t>IJ10JUNI2027</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3164,23 +3164,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP08JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ10JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MP09JANUARI2027</t>
+          <t>IJ11JUNI2027</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP09JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ11JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MP10JANUARI2027</t>
+          <t>IJ12JUNI2027</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3214,23 +3214,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP10JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ12JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MP11JANUARI2027</t>
+          <t>IJ13JUNI2027</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP11JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ13JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MP12JANUARI2027</t>
+          <t>IJ14JUNI2027</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP12JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ14JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MP13JANUARI2027</t>
+          <t>IJ15JUNI2027</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3289,23 +3289,23 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP13JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ15JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MP14JANUARI2027</t>
+          <t>IJ16JUNI2027</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3314,23 +3314,23 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP14JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ16JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MP15JANUARI2027</t>
+          <t>IJ17JUNI2027</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP15JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ17JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MP16JANUARI2027</t>
+          <t>IJ18JUNI2027</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3364,23 +3364,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP16JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ18JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MP17JANUARI2027</t>
+          <t>IJ19JUNI2027</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3389,23 +3389,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP17JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ19JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MP18JANUARI2027</t>
+          <t>IJ20JUNI2027</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3414,23 +3414,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP18JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ20JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MP19JANUARI2027</t>
+          <t>IJ21JUNI2027</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3439,23 +3439,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP19JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ21JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MP20JANUARI2027</t>
+          <t>IJ22JUNI2027</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP20JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ22JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MP21JANUARI2027</t>
+          <t>IJ23JUNI2027</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3489,23 +3489,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP21JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ23JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MP22JANUARI2027</t>
+          <t>IJ24JUNI2027</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3514,23 +3514,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP22JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ24JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MP23JANUARI2027</t>
+          <t>IJ25JUNI2027</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3539,23 +3539,23 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP23JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ25JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MP24JANUARI2027</t>
+          <t>IJ26JUNI2027</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP24JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ26JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MP25JANUARI2027</t>
+          <t>IJ27JUNI2027</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3589,23 +3589,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP25JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ27JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MP26JANUARI2027</t>
+          <t>IJ28JUNI2027</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3614,23 +3614,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP26JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ28JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MP27JANUARI2027</t>
+          <t>IJ29JUNI2027</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3639,23 +3639,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP27JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ29JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MP28JANUARI2027</t>
+          <t>IJ30JUNI2027</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>874375</v>
+        <v>874372</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3664,23 +3664,23 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP28JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/IJ30JUNI2027</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>inuJ</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MP29JANUARI2027</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>874375</v>
+        <v>14656</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP29JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/inuJ/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MP30JANUARI2027</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>874375</v>
+        <v>851</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP30JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MP31JANUARI2027</t>
+          <t>IM01MEI2027</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>874375</v>
+        <v>874371</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/MP31JANUARI2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM01MEI2027</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>markpom</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>IM02MEI2027</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>14662</v>
+        <v>874371</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/markpom/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM02MEI2027</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>IM03MEI2027</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>851</v>
+        <v>874371</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM03MEI2027</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NR01NOVEMBER2027</t>
+          <t>IM04MEI2027</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR01NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM04MEI2027</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NR02NOVEMBER2027</t>
+          <t>IM05MEI2027</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR02NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM05MEI2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NR03NOVEMBER2027</t>
+          <t>IM06MEI2027</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR03NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM06MEI2027</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NR04NOVEMBER2027</t>
+          <t>IM07MEI2027</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR04NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM07MEI2027</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NR05NOVEMBER2027</t>
+          <t>IM08MEI2027</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR05NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM08MEI2027</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NR06NOVEMBER2027</t>
+          <t>IM09MEI2027</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR06NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM09MEI2027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NR07NOVEMBER2027</t>
+          <t>IM10MEI2027</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR07NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM10MEI2027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NR08NOVEMBER2027</t>
+          <t>IM11MEI2027</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR08NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM11MEI2027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NR09NOVEMBER2027</t>
+          <t>IM12MEI2027</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR09NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM12MEI2027</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NR10NOVEMBER2027</t>
+          <t>IM13MEI2027</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR10NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM13MEI2027</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NR11NOVEMBER2027</t>
+          <t>IM14MEI2027</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR11NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM14MEI2027</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NR12NOVEMBER2027</t>
+          <t>IM15MEI2027</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR12NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM15MEI2027</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NR13NOVEMBER2027</t>
+          <t>IM16MEI2027</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR13NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM16MEI2027</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NR14NOVEMBER2027</t>
+          <t>IM17MEI2027</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR14NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM17MEI2027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NR15NOVEMBER2027</t>
+          <t>IM18MEI2027</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR15NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM18MEI2027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NR16NOVEMBER2027</t>
+          <t>IM19MEI2027</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR16NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM19MEI2027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NR17NOVEMBER2027</t>
+          <t>IM20MEI2027</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR17NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM20MEI2027</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NR18NOVEMBER2027</t>
+          <t>IM21MEI2027</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR18NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM21MEI2027</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NR19NOVEMBER2027</t>
+          <t>IM22MEI2027</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR19NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM22MEI2027</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NR20NOVEMBER2027</t>
+          <t>IM23MEI2027</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR20NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM23MEI2027</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NR21NOVEMBER2027</t>
+          <t>IM24MEI2027</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR21NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM24MEI2027</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NR22NOVEMBER2027</t>
+          <t>IM25MEI2027</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR22NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM25MEI2027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NR23NOVEMBER2027</t>
+          <t>IM26MEI2027</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR23NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM26MEI2027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NR24NOVEMBER2027</t>
+          <t>IM27MEI2027</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR24NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM27MEI2027</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NR25NOVEMBER2027</t>
+          <t>IM28MEI2027</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR25NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM28MEI2027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NR26NOVEMBER2027</t>
+          <t>IM29MEI2027</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR26NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM29MEI2027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NR27NOVEMBER2027</t>
+          <t>IM30MEI2027</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR27NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM30MEI2027</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NR28NOVEMBER2027</t>
+          <t>IM31MEI2027</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>584855</v>
+        <v>874371</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/phxnkhlay/rebmevoN/main/NR28NOVEMBER2027</t>
+          <t>https://raw.githubusercontent.com/phxnkhlay/ieM/main/IM31MEI2027</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>rebmevoN</t>
+          <t>ieM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NR29NOVEMBER2027</t>
+          <t>update_git